--- a/InputData/land/PLANAbPiaSY/cn-Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
+++ b/InputData/land/PLANAbPiaSY/cn-Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\EPS\Github Push\China\eps-china2019-smart-trans\InputData\land\PLANAbPiaSY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A6F27A-DAB3-450E-BC74-364737050F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB497826-2F59-428A-8CCA-8916745C76E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,6 +47,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2639,63 +2661,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="47" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="3" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="57" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="3" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="47" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2716,6 +2681,63 @@
     </xf>
     <xf numFmtId="177" fontId="55" fillId="38" borderId="1" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="3" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="3" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="56" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="57" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -5170,38 +5192,38 @@
       <c r="CR4" s="31"/>
     </row>
     <row r="5" spans="1:96">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="88" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="80" t="s">
+      <c r="D5" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="81" t="s">
+      <c r="E5" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
-      <c r="L5" s="83"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="92"/>
+      <c r="L5" s="93"/>
       <c r="P5" s="39" t="s">
         <v>174</v>
       </c>
       <c r="CR5" s="31"/>
     </row>
     <row r="6" spans="1:96" ht="72">
-      <c r="A6" s="77"/>
-      <c r="B6" s="77"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="77"/>
+      <c r="A6" s="87"/>
+      <c r="B6" s="87"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="87"/>
       <c r="E6" s="8" t="s">
         <v>105</v>
       </c>
@@ -6363,35 +6385,35 @@
       <c r="CR46" s="31"/>
     </row>
     <row r="47" spans="1:96">
-      <c r="A47" s="76" t="s">
+      <c r="A47" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="76" t="s">
+      <c r="B47" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="78" t="s">
+      <c r="C47" s="88" t="s">
         <v>104</v>
       </c>
-      <c r="D47" s="80" t="s">
+      <c r="D47" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="E47" s="81" t="s">
+      <c r="E47" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="F47" s="82"/>
-      <c r="G47" s="82"/>
-      <c r="H47" s="82"/>
-      <c r="I47" s="82"/>
-      <c r="J47" s="82"/>
-      <c r="K47" s="82"/>
-      <c r="L47" s="83"/>
+      <c r="F47" s="92"/>
+      <c r="G47" s="92"/>
+      <c r="H47" s="92"/>
+      <c r="I47" s="92"/>
+      <c r="J47" s="92"/>
+      <c r="K47" s="92"/>
+      <c r="L47" s="93"/>
       <c r="CR47" s="31"/>
     </row>
     <row r="48" spans="1:96" ht="72">
-      <c r="A48" s="77"/>
-      <c r="B48" s="77"/>
-      <c r="C48" s="79"/>
-      <c r="D48" s="77"/>
+      <c r="A48" s="87"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="89"/>
+      <c r="D48" s="87"/>
       <c r="E48" s="8" t="s">
         <v>105</v>
       </c>
@@ -7489,28 +7511,28 @@
       <c r="AA87" s="27"/>
     </row>
     <row r="88" spans="1:44" ht="14.65" customHeight="1">
-      <c r="A88" s="80" t="s">
+      <c r="A88" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B88" s="80" t="s">
+      <c r="B88" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="C88" s="78" t="s">
+      <c r="C88" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="D88" s="80" t="s">
+      <c r="D88" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="E88" s="84" t="s">
+      <c r="E88" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="F88" s="85"/>
-      <c r="G88" s="85"/>
-      <c r="H88" s="85"/>
-      <c r="I88" s="85"/>
-      <c r="J88" s="85"/>
-      <c r="K88" s="85"/>
-      <c r="L88" s="86"/>
+      <c r="F88" s="84"/>
+      <c r="G88" s="84"/>
+      <c r="H88" s="84"/>
+      <c r="I88" s="84"/>
+      <c r="J88" s="84"/>
+      <c r="K88" s="84"/>
+      <c r="L88" s="85"/>
       <c r="P88" s="27"/>
       <c r="Q88" s="27"/>
       <c r="R88" s="27"/>
@@ -7525,10 +7547,10 @@
       <c r="AA88" s="27"/>
     </row>
     <row r="89" spans="1:44" ht="64.150000000000006" customHeight="1">
-      <c r="A89" s="77"/>
-      <c r="B89" s="77"/>
-      <c r="C89" s="79"/>
-      <c r="D89" s="77"/>
+      <c r="A89" s="87"/>
+      <c r="B89" s="87"/>
+      <c r="C89" s="89"/>
+      <c r="D89" s="87"/>
       <c r="E89" s="8" t="s">
         <v>99</v>
       </c>
@@ -8722,21 +8744,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:L47"/>
     <mergeCell ref="E88:L88"/>
     <mergeCell ref="A88:A89"/>
     <mergeCell ref="B88:B89"/>
     <mergeCell ref="C88:C89"/>
     <mergeCell ref="D88:D89"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:L47"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:L5"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9163,31 +9185,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="14.25" customHeight="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="97" t="s">
         <v>265</v>
       </c>
-      <c r="B1" s="88" t="s">
+      <c r="B1" s="97" t="s">
         <v>264</v>
       </c>
-      <c r="C1" s="80" t="s">
+      <c r="C1" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="76" t="s">
+      <c r="D1" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="80" t="s">
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="86" t="s">
         <v>263</v>
       </c>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="95" t="s">
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="76" t="s">
         <v>266</v>
       </c>
       <c r="P1" s="55" t="s">
@@ -9195,9 +9217,9 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="72">
-      <c r="A2" s="89"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="77"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="87"/>
       <c r="D2" s="8" t="s">
         <v>105</v>
       </c>
@@ -9279,7 +9301,7 @@
         <f t="shared" ref="L3:L13" si="3">ROUND(I3*2.47,0)</f>
         <v>11834965</v>
       </c>
-      <c r="M3" s="96">
+      <c r="M3" s="77">
         <f t="shared" ref="M3:M13" si="4">ROUND(J3*2.47,0)</f>
         <v>5317606</v>
       </c>
@@ -9287,7 +9309,7 @@
         <f t="shared" ref="N3:N13" si="5">ROUND(K3*2.47,0)</f>
         <v>1826155</v>
       </c>
-      <c r="O3" s="99"/>
+      <c r="O3" s="80"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="68" t="s">
@@ -9330,7 +9352,7 @@
         <f t="shared" si="3"/>
         <v>10519194</v>
       </c>
-      <c r="M4" s="96">
+      <c r="M4" s="77">
         <f t="shared" si="4"/>
         <v>4825486</v>
       </c>
@@ -9338,7 +9360,7 @@
         <f t="shared" si="5"/>
         <v>2447987</v>
       </c>
-      <c r="O4" s="99"/>
+      <c r="O4" s="80"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="68" t="s">
@@ -9381,7 +9403,7 @@
         <f t="shared" si="3"/>
         <v>11714096</v>
       </c>
-      <c r="M5" s="96">
+      <c r="M5" s="77">
         <f t="shared" si="4"/>
         <v>4093207</v>
       </c>
@@ -9389,7 +9411,7 @@
         <f t="shared" si="5"/>
         <v>3164053</v>
       </c>
-      <c r="O5" s="99"/>
+      <c r="O5" s="80"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="68" t="s">
@@ -9432,7 +9454,7 @@
         <f t="shared" si="3"/>
         <v>10337543</v>
       </c>
-      <c r="M6" s="96">
+      <c r="M6" s="77">
         <f t="shared" si="4"/>
         <v>4409115</v>
       </c>
@@ -9440,7 +9462,7 @@
         <f t="shared" si="5"/>
         <v>3283040</v>
       </c>
-      <c r="O6" s="99"/>
+      <c r="O6" s="80"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="68" t="s">
@@ -9483,7 +9505,7 @@
         <f t="shared" si="3"/>
         <v>9766634</v>
       </c>
-      <c r="M7" s="96">
+      <c r="M7" s="77">
         <f t="shared" si="4"/>
         <v>4688836</v>
       </c>
@@ -9491,7 +9513,7 @@
         <f t="shared" si="5"/>
         <v>3798556</v>
       </c>
-      <c r="O7" s="99"/>
+      <c r="O7" s="80"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="68" t="s">
@@ -9534,7 +9556,7 @@
         <f t="shared" si="3"/>
         <v>8742417</v>
       </c>
-      <c r="M8" s="96">
+      <c r="M8" s="77">
         <f t="shared" si="4"/>
         <v>4383282</v>
       </c>
@@ -9542,7 +9564,7 @@
         <f t="shared" si="5"/>
         <v>4000531</v>
       </c>
-      <c r="O8" s="96">
+      <c r="O8" s="77">
         <f>M8</f>
         <v>4383282</v>
       </c>
@@ -9588,7 +9610,7 @@
         <f t="shared" si="3"/>
         <v>3724580</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="77">
         <f t="shared" si="4"/>
         <v>3050692</v>
       </c>
@@ -9596,7 +9618,7 @@
         <f t="shared" si="5"/>
         <v>2498032</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="77">
         <f>M9+O8</f>
         <v>7433974</v>
       </c>
@@ -9642,7 +9664,7 @@
         <f t="shared" si="3"/>
         <v>3859469</v>
       </c>
-      <c r="M10" s="96">
+      <c r="M10" s="77">
         <f t="shared" si="4"/>
         <v>2611571</v>
       </c>
@@ -9650,7 +9672,7 @@
         <f t="shared" si="5"/>
         <v>3909849</v>
       </c>
-      <c r="O10" s="96">
+      <c r="O10" s="77">
         <f t="shared" ref="O10:O13" si="6">M10+O9</f>
         <v>10045545</v>
       </c>
@@ -9696,7 +9718,7 @@
         <f t="shared" si="3"/>
         <v>4216954</v>
       </c>
-      <c r="M11" s="96">
+      <c r="M11" s="77">
         <f t="shared" si="4"/>
         <v>2798759</v>
       </c>
@@ -9704,7 +9726,7 @@
         <f t="shared" si="5"/>
         <v>4435503</v>
       </c>
-      <c r="O11" s="96">
+      <c r="O11" s="77">
         <f t="shared" si="6"/>
         <v>12844304</v>
       </c>
@@ -9750,7 +9772,7 @@
         <f t="shared" si="3"/>
         <v>3679122</v>
       </c>
-      <c r="M12" s="96">
+      <c r="M12" s="77">
         <f t="shared" si="4"/>
         <v>3129569</v>
       </c>
@@ -9758,7 +9780,7 @@
         <f t="shared" si="5"/>
         <v>4654386</v>
       </c>
-      <c r="O12" s="96">
+      <c r="O12" s="77">
         <f t="shared" si="6"/>
         <v>15973873</v>
       </c>
@@ -9808,7 +9830,7 @@
         <f t="shared" si="3"/>
         <v>3265296</v>
       </c>
-      <c r="M13" s="96">
+      <c r="M13" s="77">
         <f t="shared" si="4"/>
         <v>2225494</v>
       </c>
@@ -9816,20 +9838,20 @@
         <f t="shared" si="5"/>
         <v>3309820</v>
       </c>
-      <c r="O13" s="96">
+      <c r="O13" s="77">
         <f t="shared" si="6"/>
         <v>18199367</v>
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="M14" s="97"/>
-      <c r="O14" s="98"/>
+      <c r="M14" s="78"/>
+      <c r="O14" s="79"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="101" t="s">
         <v>262</v>
       </c>
-      <c r="B15" s="90"/>
+      <c r="B15" s="101"/>
       <c r="C15" s="72">
         <f t="shared" ref="C15:H15" si="7">MAX(C3:C13,1.25*MAX(C8:C13))</f>
         <v>8667120</v>
@@ -9870,7 +9892,7 @@
         <f>ROUND(MAX(L3:L13,1.25*MAX(L8:L13)),0)</f>
         <v>11834965</v>
       </c>
-      <c r="M15" s="96">
+      <c r="M15" s="77">
         <f t="shared" ref="M15:N15" si="9">ROUND(MAX(M3:M13,1.25*MAX(M8:M13)),0)</f>
         <v>5479103</v>
       </c>
@@ -9878,16 +9900,16 @@
         <f t="shared" si="9"/>
         <v>5817983</v>
       </c>
-      <c r="O15" s="96">
+      <c r="O15" s="77">
         <f>_xlfn.FORECAST.LINEAR(2060,O8:O13,B8:B13)</f>
         <v>115943144.28571415</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="63">
-      <c r="A17" s="94" t="s">
+      <c r="A17" s="99" t="s">
         <v>261</v>
       </c>
-      <c r="B17" s="94"/>
+      <c r="B17" s="99"/>
       <c r="C17" s="71" t="s">
         <v>259</v>
       </c>
@@ -9898,16 +9920,16 @@
         <v>257</v>
       </c>
       <c r="F17" s="65"/>
-      <c r="G17" s="87" t="s">
+      <c r="G17" s="100" t="s">
         <v>260</v>
       </c>
-      <c r="H17" s="87" t="s">
+      <c r="H17" s="100" t="s">
         <v>259</v>
       </c>
-      <c r="I17" s="87" t="s">
+      <c r="I17" s="100" t="s">
         <v>258</v>
       </c>
-      <c r="J17" s="87" t="s">
+      <c r="J17" s="100" t="s">
         <v>257</v>
       </c>
     </row>
@@ -9931,10 +9953,10 @@
         <v>0.31388100000000002</v>
       </c>
       <c r="F18" s="65"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="87"/>
-      <c r="I18" s="87"/>
-      <c r="J18" s="87"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100"/>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="68" t="s">
@@ -9956,10 +9978,10 @@
         <v>0.42076200000000002</v>
       </c>
       <c r="F19" s="65"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="87"/>
-      <c r="J19" s="87"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="100"/>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="68" t="s">
@@ -9981,10 +10003,10 @@
         <v>0.54383999999999999</v>
       </c>
       <c r="F20" s="65"/>
-      <c r="G20" s="87"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="87"/>
-      <c r="J20" s="87"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="100"/>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="68" t="s">
@@ -10006,10 +10028,10 @@
         <v>0.56429200000000002</v>
       </c>
       <c r="F21" s="65"/>
-      <c r="G21" s="87"/>
-      <c r="H21" s="87"/>
-      <c r="I21" s="87"/>
-      <c r="J21" s="87"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="100"/>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="68" t="s">
@@ -10031,12 +10053,12 @@
         <v>0.65289900000000001</v>
       </c>
       <c r="F22" s="65"/>
-      <c r="G22" s="87"/>
+      <c r="G22" s="100"/>
       <c r="H22" s="70">
         <f>MAX(C$23:C$28)</f>
         <v>0.73869399999999996</v>
       </c>
-      <c r="I22" s="100">
+      <c r="I22" s="81">
         <v>1</v>
       </c>
       <c r="J22" s="70">
@@ -10065,14 +10087,14 @@
         <v>0.68761499999999998</v>
       </c>
       <c r="F23" s="65"/>
-      <c r="G23" s="91" t="s">
+      <c r="G23" s="94" t="s">
         <v>256</v>
       </c>
       <c r="H23" s="64">
         <f t="shared" ref="H23:J28" si="13">ROUND(C23/H$22,6)</f>
         <v>1</v>
       </c>
-      <c r="I23" s="101">
+      <c r="I23" s="82">
         <f>O8/O$15</f>
         <v>3.78054435818857E-2</v>
       </c>
@@ -10101,12 +10123,12 @@
         <v>0.42936400000000002</v>
       </c>
       <c r="F24" s="65"/>
-      <c r="G24" s="92"/>
+      <c r="G24" s="95"/>
       <c r="H24" s="64">
         <f t="shared" si="13"/>
         <v>0.42603600000000003</v>
       </c>
-      <c r="I24" s="101">
+      <c r="I24" s="82">
         <f t="shared" ref="I24:I28" si="14">O9/O$15</f>
         <v>6.4117408974874349E-2</v>
       </c>
@@ -10135,12 +10157,12 @@
         <v>0.67202799999999996</v>
       </c>
       <c r="F25" s="65"/>
-      <c r="G25" s="92"/>
+      <c r="G25" s="95"/>
       <c r="H25" s="64">
         <f t="shared" si="13"/>
         <v>0.44146400000000002</v>
       </c>
-      <c r="I25" s="101">
+      <c r="I25" s="82">
         <f t="shared" si="14"/>
         <v>8.6641992175450724E-2</v>
       </c>
@@ -10169,12 +10191,12 @@
         <v>0.762378</v>
       </c>
       <c r="F26" s="65"/>
-      <c r="G26" s="92"/>
+      <c r="G26" s="95"/>
       <c r="H26" s="64">
         <f t="shared" si="13"/>
         <v>0.48235499999999998</v>
       </c>
-      <c r="I26" s="101">
+      <c r="I26" s="82">
         <f t="shared" si="14"/>
         <v>0.11078105634558508</v>
       </c>
@@ -10203,12 +10225,12 @@
         <v>0.8</v>
       </c>
       <c r="F27" s="65"/>
-      <c r="G27" s="92"/>
+      <c r="G27" s="95"/>
       <c r="H27" s="64">
         <f t="shared" si="13"/>
         <v>0.42083599999999999</v>
       </c>
-      <c r="I27" s="101">
+      <c r="I27" s="82">
         <f t="shared" si="14"/>
         <v>0.13777332931937925</v>
       </c>
@@ -10237,12 +10259,12 @@
         <v>0.56889500000000004</v>
       </c>
       <c r="F28" s="65"/>
-      <c r="G28" s="93"/>
+      <c r="G28" s="96"/>
       <c r="H28" s="64">
         <f t="shared" si="13"/>
         <v>0.3735</v>
       </c>
-      <c r="I28" s="101">
+      <c r="I28" s="82">
         <f t="shared" si="14"/>
         <v>0.15696803042663748</v>
       </c>
@@ -10258,11 +10280,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="12">
-    <mergeCell ref="G23:G28"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="G17:G22"/>
-    <mergeCell ref="H17:H21"/>
     <mergeCell ref="J17:J21"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:C2"/>
@@ -10270,6 +10287,11 @@
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="I17:I21"/>
+    <mergeCell ref="G23:G28"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="G17:G22"/>
+    <mergeCell ref="H17:H21"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="C18:E28">
@@ -16964,176 +16986,169 @@
         <v>144</v>
       </c>
       <c r="B4">
-        <f>Calculation!$M$15</f>
-        <v>5479103</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <f t="shared" si="1"/>
-        <v>5479103</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <v>0</v>
+      </c>
+      <c r="D4" cm="1">
+        <f t="array" ref="D4:I4">TRANSPOSE(Calculation!O8:O13)</f>
+        <v>4383282</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <v>7433974</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <v>10045545</v>
       </c>
       <c r="G4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <v>12844304</v>
       </c>
       <c r="H4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <v>15973873</v>
       </c>
       <c r="I4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <v>18199367</v>
       </c>
       <c r="J4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f>_xlfn.FORECAST.LINEAR(J$1,_xlfn.ANCHORARRAY($D4),$D$1:$I$1)</f>
+        <v>21229945.600000381</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" ref="K4:AR4" si="2">_xlfn.FORECAST.LINEAR(K$1,_xlfn.ANCHORARRAY($D4),$D$1:$I$1)</f>
+        <v>24015627.91428566</v>
       </c>
       <c r="L4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>26801310.228571892</v>
       </c>
       <c r="M4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>29586992.54285717</v>
       </c>
       <c r="N4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>32372674.857143402</v>
       </c>
       <c r="O4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>35158357.17142868</v>
       </c>
       <c r="P4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>37944039.485714912</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>40729721.800000191</v>
       </c>
       <c r="R4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>43515404.114286423</v>
       </c>
       <c r="S4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>46301086.428571701</v>
       </c>
       <c r="T4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>49086768.742857933</v>
       </c>
       <c r="U4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>51872451.057143211</v>
       </c>
       <c r="V4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>54658133.37142849</v>
       </c>
       <c r="W4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>57443815.685714722</v>
       </c>
       <c r="X4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>60229498</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>63015180.314286232</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>65800862.62857151</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>68586544.942857742</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>71372227.257143021</v>
       </c>
       <c r="AC4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>74157909.571429253</v>
       </c>
       <c r="AD4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>76943591.885714531</v>
       </c>
       <c r="AE4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>79729274.200000763</v>
       </c>
       <c r="AF4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>82514956.514286041</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>85300638.82857132</v>
       </c>
       <c r="AH4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>88086321.142857552</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>90872003.45714283</v>
       </c>
       <c r="AJ4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>93657685.771429062</v>
       </c>
       <c r="AK4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>96443368.08571434</v>
       </c>
       <c r="AL4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>99229050.400000572</v>
       </c>
       <c r="AM4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>102014732.71428585</v>
       </c>
       <c r="AN4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>104800415.02857208</v>
       </c>
       <c r="AO4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>107586097.34285736</v>
       </c>
       <c r="AP4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>110371779.65714359</v>
       </c>
       <c r="AQ4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>113157461.97142887</v>
       </c>
       <c r="AR4">
-        <f t="shared" si="0"/>
-        <v>5479103</v>
+        <f t="shared" si="2"/>
+        <v>115943144.28571415</v>
       </c>
     </row>
     <row r="5" spans="1:44">

--- a/InputData/land/PLANAbPiaSY/cn-Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
+++ b/InputData/land/PLANAbPiaSY/cn-Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
@@ -5,28 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\EPS\Github Push\China\eps-china2019-smart-trans\InputData\land\PLANAbPiaSY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\OneDrive\Land\PLANAbPiaSY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB497826-2F59-428A-8CCA-8916745C76E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972BE336-2A90-452C-9965-BA64D135097D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="7" xr2:uid="{50D62159-3801-4744-B2EB-993166927DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="16" r:id="rId1"/>
     <sheet name="Aforestation by province" sheetId="1" r:id="rId2"/>
     <sheet name="2020-2023national total" sheetId="14" r:id="rId3"/>
     <sheet name="set asides_2014to2018" sheetId="13" r:id="rId4"/>
-    <sheet name="Calculation" sheetId="18" r:id="rId5"/>
-    <sheet name="Yearbook Stats" sheetId="17" r:id="rId6"/>
-    <sheet name="PLANAbPiaSY" sheetId="15" r:id="rId7"/>
+    <sheet name="Forestry Statistics" sheetId="19" r:id="rId5"/>
+    <sheet name="Calculation" sheetId="18" r:id="rId6"/>
+    <sheet name="Yearbook Stats" sheetId="17" r:id="rId7"/>
+    <sheet name="PLANAbPiaSY" sheetId="15" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Calculation!$A$2:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Yearbook Stats'!$A$1:$N$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Calculation!$A$2:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Yearbook Stats'!$A$1:$N$204</definedName>
     <definedName name="acres_per_hectare">#REF!</definedName>
     <definedName name="acres_per_million_hectares">#REF!</definedName>
     <definedName name="C_to_CO2">'[1]Conversion Factors'!$A$4</definedName>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -72,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="357">
   <si>
     <t>Area of Afforestation by Region(2020)</t>
   </si>
@@ -578,22 +579,22 @@
   </si>
   <si>
     <t>afforestation, reforestation, improved management &amp; restoration</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>中国森林资源清查 (ckcest.cn)</t>
   </si>
   <si>
     <t>Forest Knowledge Service System</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Area of Land Forest by Type</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>China Environmental Statistical Yearbook</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -609,89 +610,89 @@
       </rPr>
       <t>https://forest.ckcest.cn/sd/si/zgslzy.html</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>period (2016-2050) is 35 years long, so if the policy were to</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>8-3 各地区造林情况(2021年)</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>8-3 各地区造林情况(2022年)</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>A_x000D_
 rea of Afforestation by Region (2022)</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>A_x000D_
 rea of Afforestation by Region (2021)</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>National Total</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>2013-2023</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Provincial Forestry Activity</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>2023年中国国土绿化状况公报 (people.com.cn)</t>
   </si>
   <si>
     <t>Report on the state of land greening in China 2023</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">forest set asides is the value calculated in 2018
 </t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>2021-2050</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>造林</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>更新造林</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>单位（百公顷）</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>森林抚育</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>退化林修复</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>1 hectare=2.47 acres</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>公顷到英亩</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>年份</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1161,7 +1162,7 @@
   </si>
   <si>
     <t>全国</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1174,7 +1175,7 @@
       </rPr>
       <t>治理沙化石漠化</t>
     </r>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1249,7 +1250,7 @@
       </rPr>
       <t>合计</t>
     </r>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1326,7 +1327,7 @@
       </rPr>
       <t>总面积</t>
     </r>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1342,7 +1343,7 @@
   </si>
   <si>
     <t>FOPITY Value</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1403,31 +1404,1463 @@
   </si>
   <si>
     <t>Policy Value for 14th FYP</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>Policy Action Achieved</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>Potential Maximum</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>In Acres</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>Year</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>Region</t>
-    <phoneticPr fontId="49" type="noConversion"/>
+    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>Cumulative</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>指标名称</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2000</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2001</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2002</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2003</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2004</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2005</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2006</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2007</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2008</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2009</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2010</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2011</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2012</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2013</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2014</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2015</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2016</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2017</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2018</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2019</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2020</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2021</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2022</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2023</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2024</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2025</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>总造林面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>公顷</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>造林面积（当年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>荒山）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人工造林</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>新造混交林面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>新造灌木林面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>新造竹林面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞播造林</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>荒山飞播造林面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞播营林面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人工更新（原迹地更新）面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中：人工更新面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>新造混交林面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人工促进天然更新面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>退化林修复</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>纯林改造混交林面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    (1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>低效林改造面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    (2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>退化林防护林改造面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年末实有封山育林面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无林地和疏林地封育面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有林地封育面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>灌木林封育面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中：本年新封面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无林地和疏林地新封</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有林地和灌木林地新封</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有林地新封面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>新造幼林地封山育林</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <t>零星（四旁）植树</t>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>万株</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>退耕地造林面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>森林管护面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>森林抚育总面积</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>抚育采伐</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>补植抚育</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人工促进天然更新</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其他综合抚育</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>低产（低效）林改造面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>幼林抚育</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>幼林抚育作业面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>公顷次</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>幼林抚育实际面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成林抚育面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中：中幼龄林抚育面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>抚育改造出材量</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>万立方米</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中：中幼龄林出材量</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有林地造林面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>林冠下造林</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有林地和灌木林地新封</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞播营林面积</t>
+    </r>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>林木种子采集量（吨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>育苗面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中：本年新育苗面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当年苗木产量（万株）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>母树林</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子园</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年末实有母树林面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年末实有种子园面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其他（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2002</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年起）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当年花卉种植面积（公顷）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其中：草坪面积（公顷）</t>
+    </r>
+  </si>
+  <si>
+    <t>森林（中幼龄木）抚育面积</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1439,11 +2872,19 @@
     <numFmt numFmtId="177" formatCode="0.00000_ "/>
     <numFmt numFmtId="178" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="60">
+  <fonts count="74">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1884,8 +3325,90 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0F1115"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0F1115"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F1115"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F1115"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2098,6 +3621,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2325,422 +3866,629 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="43" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="11" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="43" fillId="11" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="47">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="47" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="45" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="36" borderId="1" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="46" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="45" fillId="0" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="46" fillId="0" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="47" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="47" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="47" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="47" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="36" borderId="1" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="58" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="59" fillId="0" borderId="1" xfId="47" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="57" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="57" fillId="37" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="60" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="57" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="47" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="47" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="57" fillId="38" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="38" borderId="0" xfId="47" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="38" borderId="0" xfId="47" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="38" borderId="1" xfId="47" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="59" fillId="38" borderId="1" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="56" fillId="38" borderId="1" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="62" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="61" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="49" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="49" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="68" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="71" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="68" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="38" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="38" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="38" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="68" fillId="38" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="71" fillId="38" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="38" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="39" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="39" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="39" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="68" fillId="39" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="71" fillId="39" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="39" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="36" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="36" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="36" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="36" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="71" fillId="36" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="68" fillId="36" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="68" fillId="36" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="40" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="40" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="40" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="73" fillId="40" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="68" fillId="40" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="71" fillId="40" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="40" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="40" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="40" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="41" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="41" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="41" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="41" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="41" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="41" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="71" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="73" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="41" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="41" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="41" borderId="0" xfId="49" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="41" borderId="0" xfId="49" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="41" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="41" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="73" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="49" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="18" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="3" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="47">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="47" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="3" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="44" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="36" borderId="1" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="45" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="44" fillId="0" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="45" fillId="0" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="47" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="55" fillId="0" borderId="1" xfId="47" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="47" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="55" fillId="0" borderId="1" xfId="47" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="36" borderId="1" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="57" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="54" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="58" fillId="0" borderId="1" xfId="47" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="37" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="59" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="56" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="47" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="47" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="56" fillId="38" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="38" borderId="0" xfId="47" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" xfId="47" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="1" xfId="47" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="58" fillId="38" borderId="1" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="55" fillId="38" borderId="1" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="57" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="18" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="3" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="3" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="57" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="58" fillId="36" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="20% - 着色 1" xfId="20" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 着色 2" xfId="24" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 着色 3" xfId="28" builtinId="38" customBuiltin="1"/>
@@ -2772,6 +4520,7 @@
     <cellStyle name="常规 3" xfId="45" xr:uid="{398F77A7-4AB6-491F-AF67-8B9DF8D69362}"/>
     <cellStyle name="常规 4" xfId="46" xr:uid="{331BFF98-C758-46CE-86BB-1304D2195B94}"/>
     <cellStyle name="常规 5" xfId="47" xr:uid="{ACA7A438-5B82-4244-A6D5-5ECCEB8BF20B}"/>
+    <cellStyle name="常规 6" xfId="49" xr:uid="{9B26930D-96D4-48A7-8AB4-51549D964972}"/>
     <cellStyle name="超链接" xfId="1" builtinId="8"/>
     <cellStyle name="好" xfId="8" builtinId="26" customBuiltin="1"/>
     <cellStyle name="汇总" xfId="18" builtinId="25" customBuiltin="1"/>
@@ -3179,7 +4928,7 @@
                 <c:formatCode>#,##0_);[Red]\(#,##0\)</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>4362589</c:v>
+                  <c:v>4361827</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>3823656</c:v>
@@ -3789,7 +5538,7 @@
                 <c:formatCode>#,##0_);[Red]\(#,##0\)</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>300505</c:v>
+                  <c:v>299577</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>272805</c:v>
@@ -4575,13 +6324,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>395288</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
@@ -4640,7 +6389,7 @@
       <sheetName val="Forest Mgmt Costs"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="4">
           <cell r="A4">
             <v>3.6666666666666665</v>
@@ -5091,7 +6840,7 @@
       <c r="B29" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B23" r:id="rId1" xr:uid="{938A5F38-C549-4DA9-B527-72C64597AD73}"/>
     <hyperlink ref="B16" r:id="rId2" display="https://forest.ckcest.cn/sd/si/zgslzy.html" xr:uid="{EA2AFC86-380E-4F86-BBCB-B784E9423EB8}"/>
@@ -5192,38 +6941,38 @@
       <c r="CR4" s="31"/>
     </row>
     <row r="5" spans="1:96">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="158" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="158" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="88" t="s">
+      <c r="C5" s="156" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="86" t="s">
+      <c r="D5" s="154" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="91" t="s">
+      <c r="E5" s="159" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="92"/>
-      <c r="J5" s="92"/>
-      <c r="K5" s="92"/>
-      <c r="L5" s="93"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="160"/>
+      <c r="L5" s="161"/>
       <c r="P5" s="39" t="s">
         <v>174</v>
       </c>
       <c r="CR5" s="31"/>
     </row>
     <row r="6" spans="1:96" ht="72">
-      <c r="A6" s="87"/>
-      <c r="B6" s="87"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="87"/>
+      <c r="A6" s="155"/>
+      <c r="B6" s="155"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="155"/>
       <c r="E6" s="8" t="s">
         <v>105</v>
       </c>
@@ -6385,35 +8134,35 @@
       <c r="CR46" s="31"/>
     </row>
     <row r="47" spans="1:96">
-      <c r="A47" s="90" t="s">
+      <c r="A47" s="158" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="90" t="s">
+      <c r="B47" s="158" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="88" t="s">
+      <c r="C47" s="156" t="s">
         <v>104</v>
       </c>
-      <c r="D47" s="86" t="s">
+      <c r="D47" s="154" t="s">
         <v>76</v>
       </c>
-      <c r="E47" s="91" t="s">
+      <c r="E47" s="159" t="s">
         <v>6</v>
       </c>
-      <c r="F47" s="92"/>
-      <c r="G47" s="92"/>
-      <c r="H47" s="92"/>
-      <c r="I47" s="92"/>
-      <c r="J47" s="92"/>
-      <c r="K47" s="92"/>
-      <c r="L47" s="93"/>
+      <c r="F47" s="160"/>
+      <c r="G47" s="160"/>
+      <c r="H47" s="160"/>
+      <c r="I47" s="160"/>
+      <c r="J47" s="160"/>
+      <c r="K47" s="160"/>
+      <c r="L47" s="161"/>
       <c r="CR47" s="31"/>
     </row>
     <row r="48" spans="1:96" ht="72">
-      <c r="A48" s="87"/>
-      <c r="B48" s="87"/>
-      <c r="C48" s="89"/>
-      <c r="D48" s="87"/>
+      <c r="A48" s="155"/>
+      <c r="B48" s="155"/>
+      <c r="C48" s="157"/>
+      <c r="D48" s="155"/>
       <c r="E48" s="8" t="s">
         <v>105</v>
       </c>
@@ -7511,28 +9260,28 @@
       <c r="AA87" s="27"/>
     </row>
     <row r="88" spans="1:44" ht="14.65" customHeight="1">
-      <c r="A88" s="86" t="s">
+      <c r="A88" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="B88" s="86" t="s">
+      <c r="B88" s="154" t="s">
         <v>4</v>
       </c>
-      <c r="C88" s="88" t="s">
+      <c r="C88" s="156" t="s">
         <v>97</v>
       </c>
-      <c r="D88" s="86" t="s">
+      <c r="D88" s="154" t="s">
         <v>5</v>
       </c>
-      <c r="E88" s="83" t="s">
+      <c r="E88" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="F88" s="84"/>
-      <c r="G88" s="84"/>
-      <c r="H88" s="84"/>
-      <c r="I88" s="84"/>
-      <c r="J88" s="84"/>
-      <c r="K88" s="84"/>
-      <c r="L88" s="85"/>
+      <c r="F88" s="152"/>
+      <c r="G88" s="152"/>
+      <c r="H88" s="152"/>
+      <c r="I88" s="152"/>
+      <c r="J88" s="152"/>
+      <c r="K88" s="152"/>
+      <c r="L88" s="153"/>
       <c r="P88" s="27"/>
       <c r="Q88" s="27"/>
       <c r="R88" s="27"/>
@@ -7547,10 +9296,10 @@
       <c r="AA88" s="27"/>
     </row>
     <row r="89" spans="1:44" ht="64.150000000000006" customHeight="1">
-      <c r="A89" s="87"/>
-      <c r="B89" s="87"/>
-      <c r="C89" s="89"/>
-      <c r="D89" s="87"/>
+      <c r="A89" s="155"/>
+      <c r="B89" s="155"/>
+      <c r="C89" s="157"/>
+      <c r="D89" s="155"/>
       <c r="E89" s="8" t="s">
         <v>99</v>
       </c>
@@ -8760,7 +10509,7 @@
     <mergeCell ref="C88:C89"/>
     <mergeCell ref="D88:D89"/>
   </mergeCells>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8872,7 +10621,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9168,58 +10917,3620 @@
       <c r="A64" s="47"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18E355A2-3FBF-453E-9E99-52E3436F1B96}">
+  <dimension ref="A1:AB62"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.875" style="148" customWidth="1"/>
+    <col min="2" max="2" width="8.75" style="149" customWidth="1"/>
+    <col min="3" max="28" width="11.625" style="150" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="90"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="86" customFormat="1">
+      <c r="A1" s="82" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1" s="83"/>
+      <c r="C1" s="84" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1" s="84" t="s">
+        <v>269</v>
+      </c>
+      <c r="E1" s="84" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1" s="85" t="s">
+        <v>271</v>
+      </c>
+      <c r="G1" s="85" t="s">
+        <v>272</v>
+      </c>
+      <c r="H1" s="85" t="s">
+        <v>273</v>
+      </c>
+      <c r="I1" s="85" t="s">
+        <v>274</v>
+      </c>
+      <c r="J1" s="85" t="s">
+        <v>275</v>
+      </c>
+      <c r="K1" s="85" t="s">
+        <v>276</v>
+      </c>
+      <c r="L1" s="85" t="s">
+        <v>277</v>
+      </c>
+      <c r="M1" s="85" t="s">
+        <v>278</v>
+      </c>
+      <c r="N1" s="85" t="s">
+        <v>279</v>
+      </c>
+      <c r="O1" s="85" t="s">
+        <v>280</v>
+      </c>
+      <c r="P1" s="85" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q1" s="85" t="s">
+        <v>282</v>
+      </c>
+      <c r="R1" s="85" t="s">
+        <v>283</v>
+      </c>
+      <c r="S1" s="85" t="s">
+        <v>284</v>
+      </c>
+      <c r="T1" s="85" t="s">
+        <v>285</v>
+      </c>
+      <c r="U1" s="85" t="s">
+        <v>286</v>
+      </c>
+      <c r="V1" s="85" t="s">
+        <v>287</v>
+      </c>
+      <c r="W1" s="85" t="s">
+        <v>288</v>
+      </c>
+      <c r="X1" s="85" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y1" s="85" t="s">
+        <v>290</v>
+      </c>
+      <c r="Z1" s="85" t="s">
+        <v>291</v>
+      </c>
+      <c r="AA1" s="85" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB1" s="85" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
+      <c r="A2" s="87" t="s">
+        <v>294</v>
+      </c>
+      <c r="B2" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C2" s="89">
+        <f>C4+C8+C11+C15+C23</f>
+        <v>12154978</v>
+      </c>
+      <c r="D2" s="89">
+        <f t="shared" ref="D2:AB2" si="0">D4+D8+D11+D15+D23</f>
+        <v>11290268</v>
+      </c>
+      <c r="E2" s="89">
+        <f t="shared" si="0"/>
+        <v>10711332</v>
+      </c>
+      <c r="F2" s="89">
+        <f t="shared" si="0"/>
+        <v>11222230</v>
+      </c>
+      <c r="G2" s="89">
+        <f t="shared" si="0"/>
+        <v>7919530</v>
+      </c>
+      <c r="H2" s="89">
+        <f t="shared" si="0"/>
+        <v>6691949</v>
+      </c>
+      <c r="I2" s="89">
+        <f>I4+I8+I11+I15+I23</f>
+        <v>4597818</v>
+      </c>
+      <c r="J2" s="89">
+        <f t="shared" si="0"/>
+        <v>4682213</v>
+      </c>
+      <c r="K2" s="89">
+        <f t="shared" si="0"/>
+        <v>6007020</v>
+      </c>
+      <c r="L2" s="89">
+        <f>L4+L8+L11+L15+L23</f>
+        <v>6932683</v>
+      </c>
+      <c r="M2" s="89">
+        <f t="shared" si="0"/>
+        <v>6528293</v>
+      </c>
+      <c r="N2" s="89">
+        <f t="shared" si="0"/>
+        <v>6619742</v>
+      </c>
+      <c r="O2" s="89">
+        <f t="shared" si="0"/>
+        <v>6331892</v>
+      </c>
+      <c r="P2" s="89">
+        <f t="shared" si="0"/>
+        <v>6921777</v>
+      </c>
+      <c r="Q2" s="89">
+        <f t="shared" si="0"/>
+        <v>6308851</v>
+      </c>
+      <c r="R2" s="89">
+        <f t="shared" si="0"/>
+        <v>7682005</v>
+      </c>
+      <c r="S2" s="89">
+        <f t="shared" si="0"/>
+        <v>7203509</v>
+      </c>
+      <c r="T2" s="89">
+        <f t="shared" si="0"/>
+        <v>7680711</v>
+      </c>
+      <c r="U2" s="89">
+        <f t="shared" si="0"/>
+        <v>7299473</v>
+      </c>
+      <c r="V2" s="89">
+        <f t="shared" si="0"/>
+        <v>7390294</v>
+      </c>
+      <c r="W2" s="89">
+        <f t="shared" si="0"/>
+        <v>6933696</v>
+      </c>
+      <c r="X2" s="89">
+        <f t="shared" si="0"/>
+        <v>3754374</v>
+      </c>
+      <c r="Y2" s="89">
+        <f t="shared" si="0"/>
+        <v>4202789</v>
+      </c>
+      <c r="Z2" s="89">
+        <f t="shared" si="0"/>
+        <v>4636120</v>
+      </c>
+      <c r="AA2" s="89">
+        <f t="shared" si="0"/>
+        <v>4640922</v>
+      </c>
+      <c r="AB2" s="89">
+        <f t="shared" si="0"/>
+        <v>3563000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
+      <c r="A3" s="91" t="s">
+        <v>296</v>
+      </c>
+      <c r="B3" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C3" s="89">
+        <v>5105138</v>
+      </c>
+      <c r="D3" s="89">
+        <v>4953038</v>
+      </c>
+      <c r="E3" s="89">
+        <v>7770971</v>
+      </c>
+      <c r="F3" s="89">
+        <v>9118894</v>
+      </c>
+      <c r="G3" s="89">
+        <v>5598079</v>
+      </c>
+      <c r="H3" s="89">
+        <v>3637681</v>
+      </c>
+      <c r="I3" s="89">
+        <v>3838794</v>
+      </c>
+      <c r="J3" s="89">
+        <v>3907711</v>
+      </c>
+      <c r="K3" s="89">
+        <v>5353735</v>
+      </c>
+      <c r="L3" s="89">
+        <v>6262330</v>
+      </c>
+      <c r="M3" s="89">
+        <v>5909919</v>
+      </c>
+      <c r="N3" s="89">
+        <v>5996613</v>
+      </c>
+      <c r="O3" s="89">
+        <v>5595791</v>
+      </c>
+      <c r="P3" s="89">
+        <v>6100057</v>
+      </c>
+      <c r="Q3" s="89">
+        <v>5549612</v>
+      </c>
+      <c r="R3" s="92">
+        <v>7681952</v>
+      </c>
+      <c r="S3" s="92">
+        <v>7203509</v>
+      </c>
+      <c r="T3" s="92">
+        <v>7680711</v>
+      </c>
+      <c r="U3" s="92">
+        <v>7299473</v>
+      </c>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
+      <c r="AB3" s="93"/>
+    </row>
+    <row r="4" spans="1:28">
+      <c r="A4" s="94" t="s">
+        <v>297</v>
+      </c>
+      <c r="B4" s="95" t="s">
+        <v>295</v>
+      </c>
+      <c r="C4" s="96">
+        <v>4345008</v>
+      </c>
+      <c r="D4" s="96">
+        <v>3977324</v>
+      </c>
+      <c r="E4" s="96">
+        <v>6896041</v>
+      </c>
+      <c r="F4" s="96">
+        <v>8432486</v>
+      </c>
+      <c r="G4" s="96">
+        <v>5018885</v>
+      </c>
+      <c r="H4" s="96">
+        <v>3221295</v>
+      </c>
+      <c r="I4" s="96">
+        <v>2446122</v>
+      </c>
+      <c r="J4" s="96">
+        <v>2738521</v>
+      </c>
+      <c r="K4" s="96">
+        <v>3684261</v>
+      </c>
+      <c r="L4" s="96">
+        <v>4156293</v>
+      </c>
+      <c r="M4" s="96">
+        <v>3872762</v>
+      </c>
+      <c r="N4" s="96">
+        <v>4065693</v>
+      </c>
+      <c r="O4" s="96">
+        <v>3820704</v>
+      </c>
+      <c r="P4" s="96">
+        <v>4209686</v>
+      </c>
+      <c r="Q4" s="96">
+        <v>4052912</v>
+      </c>
+      <c r="R4" s="96">
+        <v>4361827</v>
+      </c>
+      <c r="S4" s="96">
+        <v>3823656</v>
+      </c>
+      <c r="T4" s="96">
+        <v>4295890</v>
+      </c>
+      <c r="U4" s="96">
+        <v>3677952</v>
+      </c>
+      <c r="V4" s="97">
+        <v>3458315</v>
+      </c>
+      <c r="W4" s="97">
+        <v>3000060</v>
+      </c>
+      <c r="X4" s="97">
+        <v>1085095</v>
+      </c>
+      <c r="Y4" s="97">
+        <v>930860</v>
+      </c>
+      <c r="Z4" s="97">
+        <v>1014361</v>
+      </c>
+      <c r="AA4" s="97">
+        <v>797680</v>
+      </c>
+      <c r="AB4" s="97">
+        <v>830000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
+      <c r="A5" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="B5" s="95" t="s">
+        <v>295</v>
+      </c>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="96"/>
+      <c r="L5" s="96"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="96"/>
+      <c r="O5" s="96"/>
+      <c r="P5" s="96"/>
+      <c r="Q5" s="96" t="s">
+        <v>299</v>
+      </c>
+      <c r="R5" s="96">
+        <v>1145826</v>
+      </c>
+      <c r="S5" s="96">
+        <v>765451</v>
+      </c>
+      <c r="T5" s="96">
+        <v>1416817</v>
+      </c>
+      <c r="U5" s="96">
+        <v>876206</v>
+      </c>
+      <c r="V5" s="99"/>
+      <c r="W5" s="99"/>
+      <c r="X5" s="99"/>
+      <c r="Y5" s="99"/>
+      <c r="Z5" s="99"/>
+      <c r="AA5" s="99"/>
+      <c r="AB5" s="99"/>
+    </row>
+    <row r="6" spans="1:28">
+      <c r="A6" s="98" t="s">
+        <v>300</v>
+      </c>
+      <c r="B6" s="95" t="s">
+        <v>295</v>
+      </c>
+      <c r="C6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96">
+        <v>311569</v>
+      </c>
+      <c r="R6" s="96">
+        <v>327282</v>
+      </c>
+      <c r="S6" s="96">
+        <v>293437</v>
+      </c>
+      <c r="T6" s="96">
+        <v>372593</v>
+      </c>
+      <c r="U6" s="96">
+        <v>440023</v>
+      </c>
+      <c r="V6" s="99"/>
+      <c r="W6" s="99"/>
+      <c r="X6" s="99"/>
+      <c r="Y6" s="99"/>
+      <c r="Z6" s="99"/>
+      <c r="AA6" s="99"/>
+      <c r="AB6" s="99"/>
+    </row>
+    <row r="7" spans="1:28">
+      <c r="A7" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="95" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="96">
+        <v>79800</v>
+      </c>
+      <c r="D7" s="96">
+        <v>106909</v>
+      </c>
+      <c r="E7" s="96">
+        <v>128521</v>
+      </c>
+      <c r="F7" s="96">
+        <v>178901</v>
+      </c>
+      <c r="G7" s="96">
+        <v>82058</v>
+      </c>
+      <c r="H7" s="96">
+        <v>87533</v>
+      </c>
+      <c r="I7" s="96">
+        <v>45071</v>
+      </c>
+      <c r="J7" s="96">
+        <v>64227</v>
+      </c>
+      <c r="K7" s="96">
+        <v>80711</v>
+      </c>
+      <c r="L7" s="96">
+        <v>87468</v>
+      </c>
+      <c r="M7" s="96">
+        <v>69978</v>
+      </c>
+      <c r="N7" s="96">
+        <v>74580</v>
+      </c>
+      <c r="O7" s="96">
+        <v>41424</v>
+      </c>
+      <c r="P7" s="96">
+        <v>47794</v>
+      </c>
+      <c r="Q7" s="96">
+        <v>46903</v>
+      </c>
+      <c r="R7" s="96">
+        <v>37204</v>
+      </c>
+      <c r="S7" s="96">
+        <v>31334</v>
+      </c>
+      <c r="T7" s="96">
+        <v>27319</v>
+      </c>
+      <c r="U7" s="96">
+        <v>56470</v>
+      </c>
+      <c r="V7" s="99"/>
+      <c r="W7" s="99"/>
+      <c r="X7" s="99"/>
+      <c r="Y7" s="99"/>
+      <c r="Z7" s="99"/>
+      <c r="AA7" s="99"/>
+      <c r="AB7" s="99"/>
+    </row>
+    <row r="8" spans="1:28">
+      <c r="A8" s="100" t="s">
+        <v>302</v>
+      </c>
+      <c r="B8" s="101" t="s">
+        <v>295</v>
+      </c>
+      <c r="C8" s="102">
+        <v>760130</v>
+      </c>
+      <c r="D8" s="102">
+        <v>975714</v>
+      </c>
+      <c r="E8" s="102">
+        <v>874930</v>
+      </c>
+      <c r="F8" s="102">
+        <v>686408</v>
+      </c>
+      <c r="G8" s="102">
+        <v>579194</v>
+      </c>
+      <c r="H8" s="102">
+        <v>416386</v>
+      </c>
+      <c r="I8" s="102">
+        <v>271803</v>
+      </c>
+      <c r="J8" s="102">
+        <v>118671</v>
+      </c>
+      <c r="K8" s="102">
+        <v>154065</v>
+      </c>
+      <c r="L8" s="102">
+        <v>226337</v>
+      </c>
+      <c r="M8" s="102">
+        <v>195948</v>
+      </c>
+      <c r="N8" s="102">
+        <v>196931</v>
+      </c>
+      <c r="O8" s="102">
+        <v>136409</v>
+      </c>
+      <c r="P8" s="102">
+        <v>154400</v>
+      </c>
+      <c r="Q8" s="103">
+        <v>109654</v>
+      </c>
+      <c r="R8" s="103">
+        <v>128390</v>
+      </c>
+      <c r="S8" s="103">
+        <v>162322</v>
+      </c>
+      <c r="T8" s="103">
+        <v>141220</v>
+      </c>
+      <c r="U8" s="103">
+        <v>135429</v>
+      </c>
+      <c r="V8" s="104">
+        <v>125565</v>
+      </c>
+      <c r="W8" s="104">
+        <v>151496</v>
+      </c>
+      <c r="X8" s="104">
+        <v>172239</v>
+      </c>
+      <c r="Y8" s="104">
+        <v>166099</v>
+      </c>
+      <c r="Z8" s="104">
+        <v>66997</v>
+      </c>
+      <c r="AA8" s="104">
+        <v>67612</v>
+      </c>
+      <c r="AB8" s="104">
+        <v>48080.135468960842</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
+      <c r="A9" s="100" t="s">
+        <v>303</v>
+      </c>
+      <c r="B9" s="101" t="s">
+        <v>295</v>
+      </c>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="102"/>
+      <c r="I9" s="102"/>
+      <c r="J9" s="102"/>
+      <c r="K9" s="102"/>
+      <c r="L9" s="102"/>
+      <c r="M9" s="102"/>
+      <c r="N9" s="102"/>
+      <c r="O9" s="102"/>
+      <c r="P9" s="102"/>
+      <c r="Q9" s="103">
+        <v>108055</v>
+      </c>
+      <c r="R9" s="103">
+        <v>127724</v>
+      </c>
+      <c r="S9" s="103">
+        <v>156391</v>
+      </c>
+      <c r="T9" s="103">
+        <v>136954</v>
+      </c>
+      <c r="U9" s="103">
+        <v>125907</v>
+      </c>
+      <c r="V9" s="105"/>
+      <c r="W9" s="105"/>
+      <c r="X9" s="105"/>
+      <c r="Y9" s="105"/>
+      <c r="Z9" s="105"/>
+      <c r="AA9" s="105"/>
+      <c r="AB9" s="105"/>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="A10" s="100" t="s">
+        <v>304</v>
+      </c>
+      <c r="B10" s="101" t="s">
+        <v>295</v>
+      </c>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="102">
+        <v>5022</v>
+      </c>
+      <c r="K10" s="102"/>
+      <c r="L10" s="102"/>
+      <c r="M10" s="102"/>
+      <c r="N10" s="102"/>
+      <c r="O10" s="102"/>
+      <c r="P10" s="102"/>
+      <c r="Q10" s="103">
+        <v>1599</v>
+      </c>
+      <c r="R10" s="103">
+        <v>666</v>
+      </c>
+      <c r="S10" s="103">
+        <v>5931</v>
+      </c>
+      <c r="T10" s="103">
+        <v>4266</v>
+      </c>
+      <c r="U10" s="103">
+        <v>9522</v>
+      </c>
+      <c r="V10" s="105"/>
+      <c r="W10" s="105"/>
+      <c r="X10" s="105"/>
+      <c r="Y10" s="105"/>
+      <c r="Z10" s="105"/>
+      <c r="AA10" s="105"/>
+      <c r="AB10" s="105"/>
+    </row>
+    <row r="11" spans="1:28">
+      <c r="A11" s="106" t="s">
+        <v>305</v>
+      </c>
+      <c r="B11" s="107" t="s">
+        <v>295</v>
+      </c>
+      <c r="C11" s="108">
+        <v>919799</v>
+      </c>
+      <c r="D11" s="108">
+        <v>515293</v>
+      </c>
+      <c r="E11" s="108">
+        <v>378999</v>
+      </c>
+      <c r="F11" s="108">
+        <v>285994</v>
+      </c>
+      <c r="G11" s="108">
+        <v>319310</v>
+      </c>
+      <c r="H11" s="108">
+        <v>407546</v>
+      </c>
+      <c r="I11" s="108">
+        <v>408240</v>
+      </c>
+      <c r="J11" s="108">
+        <v>390911</v>
+      </c>
+      <c r="K11" s="108">
+        <v>424003</v>
+      </c>
+      <c r="L11" s="108">
+        <v>344254</v>
+      </c>
+      <c r="M11" s="108">
+        <v>306708</v>
+      </c>
+      <c r="N11" s="108">
+        <v>326641</v>
+      </c>
+      <c r="O11" s="108">
+        <v>305065</v>
+      </c>
+      <c r="P11" s="108">
+        <v>303086</v>
+      </c>
+      <c r="Q11" s="108">
+        <v>292453</v>
+      </c>
+      <c r="R11" s="109">
+        <v>299577</v>
+      </c>
+      <c r="S11" s="109">
+        <v>272805</v>
+      </c>
+      <c r="T11" s="109">
+        <v>305439</v>
+      </c>
+      <c r="U11" s="109">
+        <v>371859</v>
+      </c>
+      <c r="V11" s="110">
+        <v>370223</v>
+      </c>
+      <c r="W11" s="110">
+        <v>387884</v>
+      </c>
+      <c r="X11" s="110">
+        <v>250593</v>
+      </c>
+      <c r="Y11" s="110">
+        <v>465579</v>
+      </c>
+      <c r="Z11" s="110">
+        <v>625911</v>
+      </c>
+      <c r="AA11" s="110">
+        <v>624231</v>
+      </c>
+      <c r="AB11" s="110">
+        <v>443902.13340715988</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
+      <c r="A12" s="106" t="s">
+        <v>306</v>
+      </c>
+      <c r="B12" s="107" t="s">
+        <v>295</v>
+      </c>
+      <c r="C12" s="108">
+        <v>568309</v>
+      </c>
+      <c r="D12" s="108">
+        <v>386571</v>
+      </c>
+      <c r="E12" s="108">
+        <v>298369</v>
+      </c>
+      <c r="F12" s="108">
+        <v>220866</v>
+      </c>
+      <c r="G12" s="108">
+        <v>271262</v>
+      </c>
+      <c r="H12" s="108">
+        <v>326952</v>
+      </c>
+      <c r="I12" s="108">
+        <v>300202</v>
+      </c>
+      <c r="J12" s="108" t="s">
+        <v>307</v>
+      </c>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="111"/>
+      <c r="P12" s="111"/>
+      <c r="Q12" s="111"/>
+      <c r="R12" s="111"/>
+      <c r="S12" s="111"/>
+      <c r="T12" s="111"/>
+      <c r="U12" s="111"/>
+      <c r="V12" s="111"/>
+      <c r="W12" s="111"/>
+      <c r="X12" s="111"/>
+      <c r="Y12" s="111"/>
+      <c r="Z12" s="111"/>
+      <c r="AA12" s="111"/>
+      <c r="AB12" s="111"/>
+    </row>
+    <row r="13" spans="1:28">
+      <c r="A13" s="106" t="s">
+        <v>308</v>
+      </c>
+      <c r="B13" s="107" t="s">
+        <v>295</v>
+      </c>
+      <c r="C13" s="108"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="108"/>
+      <c r="H13" s="108"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="108"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="111"/>
+      <c r="N13" s="111"/>
+      <c r="O13" s="111"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="111"/>
+      <c r="R13" s="111">
+        <v>54541</v>
+      </c>
+      <c r="S13" s="111">
+        <v>44782</v>
+      </c>
+      <c r="T13" s="111">
+        <v>45936</v>
+      </c>
+      <c r="U13" s="111">
+        <v>31913</v>
+      </c>
+      <c r="V13" s="111"/>
+      <c r="W13" s="111"/>
+      <c r="X13" s="111"/>
+      <c r="Y13" s="111"/>
+      <c r="Z13" s="111"/>
+      <c r="AA13" s="111"/>
+      <c r="AB13" s="111"/>
+    </row>
+    <row r="14" spans="1:28">
+      <c r="A14" s="106" t="s">
+        <v>309</v>
+      </c>
+      <c r="B14" s="107" t="s">
+        <v>295</v>
+      </c>
+      <c r="C14" s="108"/>
+      <c r="D14" s="108"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="108"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="108"/>
+      <c r="I14" s="108"/>
+      <c r="J14" s="108"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="111">
+        <v>56825</v>
+      </c>
+      <c r="S14" s="111">
+        <v>46979</v>
+      </c>
+      <c r="T14" s="111">
+        <v>36295</v>
+      </c>
+      <c r="U14" s="111">
+        <v>189794</v>
+      </c>
+      <c r="V14" s="111"/>
+      <c r="W14" s="111"/>
+      <c r="X14" s="111"/>
+      <c r="Y14" s="111"/>
+      <c r="Z14" s="111"/>
+      <c r="AA14" s="111"/>
+      <c r="AB14" s="111"/>
+    </row>
+    <row r="15" spans="1:28">
+      <c r="A15" s="112" t="s">
+        <v>310</v>
+      </c>
+      <c r="B15" s="113" t="s">
+        <v>295</v>
+      </c>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="114"/>
+      <c r="J15" s="114"/>
+      <c r="K15" s="115"/>
+      <c r="L15" s="115"/>
+      <c r="M15" s="115"/>
+      <c r="N15" s="115"/>
+      <c r="O15" s="115"/>
+      <c r="P15" s="115"/>
+      <c r="Q15" s="115"/>
+      <c r="R15" s="116">
+        <v>739334</v>
+      </c>
+      <c r="S15" s="116">
+        <v>991088</v>
+      </c>
+      <c r="T15" s="116">
+        <v>1280993</v>
+      </c>
+      <c r="U15" s="116">
+        <v>1329166</v>
+      </c>
+      <c r="V15" s="116">
+        <v>1537877</v>
+      </c>
+      <c r="W15" s="116">
+        <v>1619648</v>
+      </c>
+      <c r="X15" s="116">
+        <v>1011349</v>
+      </c>
+      <c r="Y15" s="116">
+        <v>1582935</v>
+      </c>
+      <c r="Z15" s="116">
+        <v>1795750</v>
+      </c>
+      <c r="AA15" s="116">
+        <v>1884367</v>
+      </c>
+      <c r="AB15" s="116">
+        <v>1340007.9961136978</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
+      <c r="A16" s="117" t="s">
+        <v>311</v>
+      </c>
+      <c r="B16" s="113" t="s">
+        <v>295</v>
+      </c>
+      <c r="C16" s="114"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="114"/>
+      <c r="H16" s="114"/>
+      <c r="I16" s="114"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="115"/>
+      <c r="L16" s="115"/>
+      <c r="M16" s="115"/>
+      <c r="N16" s="115"/>
+      <c r="O16" s="115"/>
+      <c r="P16" s="115"/>
+      <c r="Q16" s="115"/>
+      <c r="R16" s="118">
+        <v>29491</v>
+      </c>
+      <c r="S16" s="118">
+        <v>46291</v>
+      </c>
+      <c r="T16" s="118">
+        <v>93056</v>
+      </c>
+      <c r="U16" s="118">
+        <v>69309</v>
+      </c>
+      <c r="V16" s="116"/>
+      <c r="W16" s="116"/>
+      <c r="X16" s="116"/>
+      <c r="Y16" s="116"/>
+      <c r="Z16" s="116"/>
+      <c r="AA16" s="116"/>
+      <c r="AB16" s="116"/>
+    </row>
+    <row r="17" spans="1:28">
+      <c r="A17" s="117" t="s">
+        <v>312</v>
+      </c>
+      <c r="B17" s="113" t="s">
+        <v>295</v>
+      </c>
+      <c r="C17" s="114">
+        <v>1073420</v>
+      </c>
+      <c r="D17" s="114">
+        <v>703774</v>
+      </c>
+      <c r="E17" s="114">
+        <v>575934</v>
+      </c>
+      <c r="F17" s="114">
+        <v>264040</v>
+      </c>
+      <c r="G17" s="114">
+        <v>279516</v>
+      </c>
+      <c r="H17" s="114">
+        <v>328060</v>
+      </c>
+      <c r="I17" s="114">
+        <v>296056</v>
+      </c>
+      <c r="J17" s="114">
+        <v>290609</v>
+      </c>
+      <c r="K17" s="114">
+        <v>395861</v>
+      </c>
+      <c r="L17" s="114">
+        <v>543412</v>
+      </c>
+      <c r="M17" s="114">
+        <v>665598</v>
+      </c>
+      <c r="N17" s="114">
+        <v>788810</v>
+      </c>
+      <c r="O17" s="114">
+        <v>707499</v>
+      </c>
+      <c r="P17" s="114">
+        <v>758327</v>
+      </c>
+      <c r="Q17" s="114">
+        <v>687375</v>
+      </c>
+      <c r="R17" s="118">
+        <v>684752</v>
+      </c>
+      <c r="S17" s="118">
+        <v>718305</v>
+      </c>
+      <c r="T17" s="118">
+        <v>764190</v>
+      </c>
+      <c r="U17" s="118">
+        <v>846156</v>
+      </c>
+      <c r="V17" s="116"/>
+      <c r="W17" s="116"/>
+      <c r="X17" s="116"/>
+      <c r="Y17" s="116"/>
+      <c r="Z17" s="116"/>
+      <c r="AA17" s="116"/>
+      <c r="AB17" s="116"/>
+    </row>
+    <row r="18" spans="1:28">
+      <c r="A18" s="117" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" s="113" t="s">
+        <v>295</v>
+      </c>
+      <c r="C18" s="114"/>
+      <c r="D18" s="114"/>
+      <c r="E18" s="114"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="114"/>
+      <c r="H18" s="114"/>
+      <c r="I18" s="114"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="115"/>
+      <c r="L18" s="115"/>
+      <c r="M18" s="115"/>
+      <c r="N18" s="115"/>
+      <c r="O18" s="115"/>
+      <c r="P18" s="115"/>
+      <c r="Q18" s="115"/>
+      <c r="R18" s="118">
+        <v>54529</v>
+      </c>
+      <c r="S18" s="118">
+        <v>272783</v>
+      </c>
+      <c r="T18" s="118">
+        <v>516803</v>
+      </c>
+      <c r="U18" s="118">
+        <v>483010</v>
+      </c>
+      <c r="V18" s="116"/>
+      <c r="W18" s="116"/>
+      <c r="X18" s="116"/>
+      <c r="Y18" s="116"/>
+      <c r="Z18" s="116"/>
+      <c r="AA18" s="116"/>
+      <c r="AB18" s="116"/>
+    </row>
+    <row r="19" spans="1:28">
+      <c r="A19" s="91" t="s">
+        <v>314</v>
+      </c>
+      <c r="B19" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C19" s="89">
+        <v>32584372</v>
+      </c>
+      <c r="D19" s="89">
+        <v>35426636</v>
+      </c>
+      <c r="E19" s="89">
+        <v>29301513</v>
+      </c>
+      <c r="F19" s="89">
+        <v>23055394</v>
+      </c>
+      <c r="G19" s="89">
+        <v>21585588</v>
+      </c>
+      <c r="H19" s="89">
+        <v>21994790</v>
+      </c>
+      <c r="I19" s="89">
+        <v>20202327</v>
+      </c>
+      <c r="J19" s="89">
+        <v>20643218</v>
+      </c>
+      <c r="K19" s="89">
+        <v>21526252</v>
+      </c>
+      <c r="L19" s="89">
+        <v>21537816</v>
+      </c>
+      <c r="M19" s="89">
+        <v>23938134</v>
+      </c>
+      <c r="N19" s="89">
+        <v>23481113</v>
+      </c>
+      <c r="O19" s="89">
+        <v>24140908</v>
+      </c>
+      <c r="P19" s="89">
+        <v>25178730</v>
+      </c>
+      <c r="Q19" s="89">
+        <v>24719474</v>
+      </c>
+      <c r="R19" s="92">
+        <v>27509897</v>
+      </c>
+      <c r="S19" s="92">
+        <v>25497053</v>
+      </c>
+      <c r="T19" s="92">
+        <v>24682804</v>
+      </c>
+      <c r="U19" s="92">
+        <v>24596091</v>
+      </c>
+      <c r="V19" s="93"/>
+      <c r="W19" s="93"/>
+      <c r="X19" s="93"/>
+      <c r="Y19" s="93"/>
+      <c r="Z19" s="93"/>
+      <c r="AA19" s="93"/>
+      <c r="AB19" s="93"/>
+    </row>
+    <row r="20" spans="1:28">
+      <c r="A20" s="119" t="s">
+        <v>315</v>
+      </c>
+      <c r="B20" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89">
+        <v>9002889</v>
+      </c>
+      <c r="H20" s="89">
+        <v>9992981</v>
+      </c>
+      <c r="I20" s="89">
+        <v>9433425</v>
+      </c>
+      <c r="J20" s="89"/>
+      <c r="K20" s="89"/>
+      <c r="L20" s="89"/>
+      <c r="M20" s="89"/>
+      <c r="N20" s="89"/>
+      <c r="O20" s="89"/>
+      <c r="P20" s="89"/>
+      <c r="Q20" s="89"/>
+      <c r="R20" s="92"/>
+      <c r="S20" s="92"/>
+      <c r="T20" s="92"/>
+      <c r="U20" s="92"/>
+      <c r="V20" s="93"/>
+      <c r="W20" s="93"/>
+      <c r="X20" s="93"/>
+      <c r="Y20" s="93"/>
+      <c r="Z20" s="93"/>
+      <c r="AA20" s="93"/>
+      <c r="AB20" s="93"/>
+    </row>
+    <row r="21" spans="1:28">
+      <c r="A21" s="119" t="s">
+        <v>316</v>
+      </c>
+      <c r="B21" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C21" s="89"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="89">
+        <v>7432555</v>
+      </c>
+      <c r="H21" s="89">
+        <v>7272836</v>
+      </c>
+      <c r="I21" s="89">
+        <v>6526637</v>
+      </c>
+      <c r="J21" s="89"/>
+      <c r="K21" s="89"/>
+      <c r="L21" s="89"/>
+      <c r="M21" s="89"/>
+      <c r="N21" s="89"/>
+      <c r="O21" s="89"/>
+      <c r="P21" s="89"/>
+      <c r="Q21" s="89"/>
+      <c r="R21" s="92"/>
+      <c r="S21" s="92"/>
+      <c r="T21" s="92"/>
+      <c r="U21" s="92"/>
+      <c r="V21" s="93"/>
+      <c r="W21" s="93"/>
+      <c r="X21" s="93"/>
+      <c r="Y21" s="93"/>
+      <c r="Z21" s="93"/>
+      <c r="AA21" s="93"/>
+      <c r="AB21" s="93"/>
+    </row>
+    <row r="22" spans="1:28">
+      <c r="A22" s="119" t="s">
+        <v>317</v>
+      </c>
+      <c r="B22" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="89">
+        <v>5150144</v>
+      </c>
+      <c r="H22" s="89">
+        <v>4728972</v>
+      </c>
+      <c r="I22" s="89">
+        <v>4242265</v>
+      </c>
+      <c r="J22" s="89"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="89"/>
+      <c r="N22" s="89"/>
+      <c r="O22" s="89"/>
+      <c r="P22" s="89"/>
+      <c r="Q22" s="89"/>
+      <c r="R22" s="92"/>
+      <c r="S22" s="92"/>
+      <c r="T22" s="92"/>
+      <c r="U22" s="92"/>
+      <c r="V22" s="93"/>
+      <c r="W22" s="93"/>
+      <c r="X22" s="93"/>
+      <c r="Y22" s="93"/>
+      <c r="Z22" s="93"/>
+      <c r="AA22" s="93"/>
+      <c r="AB22" s="93"/>
+    </row>
+    <row r="23" spans="1:28">
+      <c r="A23" s="120" t="s">
+        <v>318</v>
+      </c>
+      <c r="B23" s="121" t="s">
+        <v>295</v>
+      </c>
+      <c r="C23" s="122">
+        <v>6130041</v>
+      </c>
+      <c r="D23" s="122">
+        <v>5821937</v>
+      </c>
+      <c r="E23" s="122">
+        <v>2561362</v>
+      </c>
+      <c r="F23" s="122">
+        <v>1817342</v>
+      </c>
+      <c r="G23" s="122">
+        <v>2002141</v>
+      </c>
+      <c r="H23" s="122">
+        <v>2646722</v>
+      </c>
+      <c r="I23" s="122">
+        <v>1471653</v>
+      </c>
+      <c r="J23" s="123">
+        <f>J24+J25+J28</f>
+        <v>1434110</v>
+      </c>
+      <c r="K23" s="123">
+        <f t="shared" ref="K23:P23" si="1">K24+K25+K28</f>
+        <v>1744691</v>
+      </c>
+      <c r="L23" s="123">
+        <f t="shared" si="1"/>
+        <v>2205799</v>
+      </c>
+      <c r="M23" s="123">
+        <f t="shared" si="1"/>
+        <v>2152875</v>
+      </c>
+      <c r="N23" s="123">
+        <f t="shared" si="1"/>
+        <v>2030477</v>
+      </c>
+      <c r="O23" s="123">
+        <f t="shared" si="1"/>
+        <v>2069714</v>
+      </c>
+      <c r="P23" s="123">
+        <f t="shared" si="1"/>
+        <v>2254605</v>
+      </c>
+      <c r="Q23" s="124">
+        <v>1853832</v>
+      </c>
+      <c r="R23" s="124">
+        <v>2152877</v>
+      </c>
+      <c r="S23" s="124">
+        <v>1953638</v>
+      </c>
+      <c r="T23" s="124">
+        <v>1657169</v>
+      </c>
+      <c r="U23" s="124">
+        <v>1785067</v>
+      </c>
+      <c r="V23" s="125">
+        <v>1898314</v>
+      </c>
+      <c r="W23" s="125">
+        <v>1774608</v>
+      </c>
+      <c r="X23" s="125">
+        <v>1235098</v>
+      </c>
+      <c r="Y23" s="125">
+        <v>1057316</v>
+      </c>
+      <c r="Z23" s="125">
+        <v>1133101</v>
+      </c>
+      <c r="AA23" s="125">
+        <v>1267032</v>
+      </c>
+      <c r="AB23" s="125">
+        <v>901009.73501018144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28">
+      <c r="A24" s="126" t="s">
+        <v>319</v>
+      </c>
+      <c r="B24" s="121" t="s">
+        <v>295</v>
+      </c>
+      <c r="C24" s="122">
+        <v>6130041</v>
+      </c>
+      <c r="D24" s="122">
+        <v>5821937</v>
+      </c>
+      <c r="E24" s="122">
+        <v>2561362</v>
+      </c>
+      <c r="F24" s="122">
+        <v>1817342</v>
+      </c>
+      <c r="G24" s="122">
+        <v>1196546</v>
+      </c>
+      <c r="H24" s="122">
+        <v>1762999</v>
+      </c>
+      <c r="I24" s="122">
+        <v>1120869</v>
+      </c>
+      <c r="J24" s="122">
+        <v>1050519</v>
+      </c>
+      <c r="K24" s="122">
+        <v>1515409</v>
+      </c>
+      <c r="L24" s="122">
+        <v>1879700</v>
+      </c>
+      <c r="M24" s="122">
+        <v>1841209</v>
+      </c>
+      <c r="N24" s="122">
+        <v>1733989</v>
+      </c>
+      <c r="O24" s="122">
+        <v>1638678</v>
+      </c>
+      <c r="P24" s="122">
+        <v>1735971</v>
+      </c>
+      <c r="Q24" s="122">
+        <v>1388645</v>
+      </c>
+      <c r="R24" s="124">
+        <v>1544074</v>
+      </c>
+      <c r="S24" s="124">
+        <v>1399471</v>
+      </c>
+      <c r="T24" s="124">
+        <v>984741</v>
+      </c>
+      <c r="U24" s="124">
+        <v>1034079</v>
+      </c>
+      <c r="V24" s="127">
+        <v>1072561</v>
+      </c>
+      <c r="W24" s="127">
+        <v>1025026</v>
+      </c>
+      <c r="X24" s="127"/>
+      <c r="Y24" s="127"/>
+      <c r="Z24" s="127"/>
+      <c r="AA24" s="127"/>
+      <c r="AB24" s="127"/>
+    </row>
+    <row r="25" spans="1:28">
+      <c r="A25" s="126" t="s">
+        <v>320</v>
+      </c>
+      <c r="B25" s="121" t="s">
+        <v>295</v>
+      </c>
+      <c r="C25" s="122" t="s">
+        <v>307</v>
+      </c>
+      <c r="D25" s="122" t="s">
+        <v>307</v>
+      </c>
+      <c r="E25" s="122" t="s">
+        <v>307</v>
+      </c>
+      <c r="F25" s="122" t="s">
+        <v>307</v>
+      </c>
+      <c r="G25" s="123">
+        <f>G26+G27</f>
+        <v>805595</v>
+      </c>
+      <c r="H25" s="123">
+        <f>H26+H27</f>
+        <v>883723</v>
+      </c>
+      <c r="I25" s="123">
+        <f>I26+I27</f>
+        <v>350784</v>
+      </c>
+      <c r="J25" s="122">
+        <v>383591</v>
+      </c>
+      <c r="K25" s="122">
+        <v>229282</v>
+      </c>
+      <c r="L25" s="122">
+        <v>326099</v>
+      </c>
+      <c r="M25" s="122">
+        <v>311666</v>
+      </c>
+      <c r="N25" s="122">
+        <v>296488</v>
+      </c>
+      <c r="O25" s="122">
+        <v>431036</v>
+      </c>
+      <c r="P25" s="122">
+        <v>518634</v>
+      </c>
+      <c r="Q25" s="124">
+        <v>465187</v>
+      </c>
+      <c r="R25" s="124">
+        <v>608803</v>
+      </c>
+      <c r="S25" s="124">
+        <v>554167</v>
+      </c>
+      <c r="T25" s="124">
+        <v>672428</v>
+      </c>
+      <c r="U25" s="124">
+        <v>750988</v>
+      </c>
+      <c r="V25" s="127">
+        <v>781476</v>
+      </c>
+      <c r="W25" s="127">
+        <v>680500</v>
+      </c>
+      <c r="X25" s="127"/>
+      <c r="Y25" s="127"/>
+      <c r="Z25" s="127"/>
+      <c r="AA25" s="127"/>
+      <c r="AB25" s="127"/>
+    </row>
+    <row r="26" spans="1:28">
+      <c r="A26" s="128" t="s">
+        <v>321</v>
+      </c>
+      <c r="B26" s="121" t="s">
+        <v>295</v>
+      </c>
+      <c r="C26" s="122"/>
+      <c r="D26" s="122"/>
+      <c r="E26" s="122"/>
+      <c r="F26" s="122"/>
+      <c r="G26" s="122">
+        <v>518419</v>
+      </c>
+      <c r="H26" s="122">
+        <v>546220</v>
+      </c>
+      <c r="I26" s="122">
+        <v>244278</v>
+      </c>
+      <c r="J26" s="127"/>
+      <c r="K26" s="127"/>
+      <c r="L26" s="127"/>
+      <c r="M26" s="127"/>
+      <c r="N26" s="127"/>
+      <c r="O26" s="127"/>
+      <c r="P26" s="127"/>
+      <c r="Q26" s="127"/>
+      <c r="R26" s="127"/>
+      <c r="S26" s="127"/>
+      <c r="T26" s="127"/>
+      <c r="U26" s="127"/>
+      <c r="V26" s="127"/>
+      <c r="W26" s="127"/>
+      <c r="X26" s="127"/>
+      <c r="Y26" s="127"/>
+      <c r="Z26" s="127"/>
+      <c r="AA26" s="127"/>
+      <c r="AB26" s="127"/>
+    </row>
+    <row r="27" spans="1:28">
+      <c r="A27" s="128" t="s">
+        <v>317</v>
+      </c>
+      <c r="B27" s="121" t="s">
+        <v>295</v>
+      </c>
+      <c r="C27" s="122"/>
+      <c r="D27" s="122"/>
+      <c r="E27" s="122"/>
+      <c r="F27" s="122"/>
+      <c r="G27" s="122">
+        <v>287176</v>
+      </c>
+      <c r="H27" s="122">
+        <v>337503</v>
+      </c>
+      <c r="I27" s="122">
+        <v>106506</v>
+      </c>
+      <c r="J27" s="127"/>
+      <c r="K27" s="127"/>
+      <c r="L27" s="127"/>
+      <c r="M27" s="127"/>
+      <c r="N27" s="127"/>
+      <c r="O27" s="127"/>
+      <c r="P27" s="127"/>
+      <c r="Q27" s="127"/>
+      <c r="R27" s="127"/>
+      <c r="S27" s="127"/>
+      <c r="T27" s="127"/>
+      <c r="U27" s="127"/>
+      <c r="V27" s="127"/>
+      <c r="W27" s="127"/>
+      <c r="X27" s="127"/>
+      <c r="Y27" s="127"/>
+      <c r="Z27" s="127"/>
+      <c r="AA27" s="127"/>
+      <c r="AB27" s="127"/>
+    </row>
+    <row r="28" spans="1:28">
+      <c r="A28" s="128" t="s">
+        <v>322</v>
+      </c>
+      <c r="B28" s="121" t="s">
+        <v>295</v>
+      </c>
+      <c r="C28" s="122"/>
+      <c r="D28" s="122"/>
+      <c r="E28" s="122"/>
+      <c r="F28" s="122"/>
+      <c r="G28" s="122"/>
+      <c r="H28" s="122"/>
+      <c r="I28" s="122"/>
+      <c r="J28" s="122"/>
+      <c r="K28" s="127"/>
+      <c r="L28" s="127"/>
+      <c r="M28" s="127"/>
+      <c r="N28" s="127"/>
+      <c r="O28" s="127"/>
+      <c r="P28" s="127"/>
+      <c r="Q28" s="127"/>
+      <c r="R28" s="127"/>
+      <c r="S28" s="127"/>
+      <c r="T28" s="127"/>
+      <c r="U28" s="127"/>
+      <c r="V28" s="127">
+        <v>44277</v>
+      </c>
+      <c r="W28" s="127">
+        <v>69082</v>
+      </c>
+      <c r="X28" s="127"/>
+      <c r="Y28" s="127"/>
+      <c r="Z28" s="127"/>
+      <c r="AA28" s="127"/>
+      <c r="AB28" s="127"/>
+    </row>
+    <row r="29" spans="1:28">
+      <c r="A29" s="129"/>
+      <c r="B29" s="130"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="131"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="132"/>
+      <c r="L29" s="132"/>
+      <c r="M29" s="132"/>
+      <c r="N29" s="132"/>
+      <c r="O29" s="132"/>
+      <c r="P29" s="132"/>
+      <c r="Q29" s="132"/>
+      <c r="R29" s="132"/>
+      <c r="S29" s="132"/>
+      <c r="T29" s="132"/>
+      <c r="U29" s="132"/>
+      <c r="V29" s="132"/>
+      <c r="W29" s="132"/>
+      <c r="X29" s="132"/>
+      <c r="Y29" s="132"/>
+      <c r="Z29" s="132"/>
+      <c r="AA29" s="132"/>
+      <c r="AB29" s="132"/>
+    </row>
+    <row r="30" spans="1:28">
+      <c r="A30" s="133" t="s">
+        <v>323</v>
+      </c>
+      <c r="B30" s="88" t="s">
+        <v>324</v>
+      </c>
+      <c r="C30" s="89">
+        <v>300504</v>
+      </c>
+      <c r="D30" s="89">
+        <v>280448</v>
+      </c>
+      <c r="E30" s="89">
+        <v>264031</v>
+      </c>
+      <c r="F30" s="89">
+        <v>301341</v>
+      </c>
+      <c r="G30" s="89">
+        <v>271139</v>
+      </c>
+      <c r="H30" s="89">
+        <v>214246</v>
+      </c>
+      <c r="I30" s="89">
+        <v>232487</v>
+      </c>
+      <c r="J30" s="89">
+        <v>245438</v>
+      </c>
+      <c r="K30" s="89">
+        <v>235499</v>
+      </c>
+      <c r="L30" s="89">
+        <v>245555</v>
+      </c>
+      <c r="M30" s="89">
+        <v>246930</v>
+      </c>
+      <c r="N30" s="89">
+        <v>245776</v>
+      </c>
+      <c r="O30" s="89">
+        <v>239418</v>
+      </c>
+      <c r="P30" s="89">
+        <v>235734</v>
+      </c>
+      <c r="Q30" s="89">
+        <v>205721</v>
+      </c>
+      <c r="R30" s="92">
+        <v>212374</v>
+      </c>
+      <c r="S30" s="92">
+        <v>183094</v>
+      </c>
+      <c r="T30" s="92">
+        <v>174799</v>
+      </c>
+      <c r="U30" s="92">
+        <v>173967</v>
+      </c>
+      <c r="V30" s="93"/>
+      <c r="W30" s="93"/>
+      <c r="X30" s="93"/>
+      <c r="Y30" s="93"/>
+      <c r="Z30" s="93"/>
+      <c r="AA30" s="93"/>
+      <c r="AB30" s="93"/>
+    </row>
+    <row r="31" spans="1:28">
+      <c r="A31" s="91" t="s">
+        <v>325</v>
+      </c>
+      <c r="B31" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C31" s="89">
+        <v>751731</v>
+      </c>
+      <c r="D31" s="89">
+        <v>653269</v>
+      </c>
+      <c r="E31" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="F31" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="G31" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="H31" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="I31" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="J31" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="K31" s="93"/>
+      <c r="L31" s="93"/>
+      <c r="M31" s="93"/>
+      <c r="N31" s="93"/>
+      <c r="O31" s="93"/>
+      <c r="P31" s="93"/>
+      <c r="Q31" s="93"/>
+      <c r="R31" s="93"/>
+      <c r="S31" s="93"/>
+      <c r="T31" s="93"/>
+      <c r="U31" s="93"/>
+      <c r="V31" s="93"/>
+      <c r="W31" s="93"/>
+      <c r="X31" s="93"/>
+      <c r="Y31" s="93"/>
+      <c r="Z31" s="93"/>
+      <c r="AA31" s="93"/>
+      <c r="AB31" s="93"/>
+    </row>
+    <row r="32" spans="1:28">
+      <c r="A32" s="91" t="s">
+        <v>326</v>
+      </c>
+      <c r="B32" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C32" s="89">
+        <v>21514468</v>
+      </c>
+      <c r="D32" s="89">
+        <v>120225687</v>
+      </c>
+      <c r="E32" s="89">
+        <v>134058184</v>
+      </c>
+      <c r="F32" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="G32" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="H32" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="I32" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="J32" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="K32" s="93"/>
+      <c r="L32" s="93"/>
+      <c r="M32" s="93"/>
+      <c r="N32" s="93"/>
+      <c r="O32" s="93"/>
+      <c r="P32" s="93"/>
+      <c r="Q32" s="93"/>
+      <c r="R32" s="93"/>
+      <c r="S32" s="93"/>
+      <c r="T32" s="93"/>
+      <c r="U32" s="93"/>
+      <c r="V32" s="93"/>
+      <c r="W32" s="93"/>
+      <c r="X32" s="93"/>
+      <c r="Y32" s="93"/>
+      <c r="Z32" s="93"/>
+      <c r="AA32" s="93"/>
+      <c r="AB32" s="93"/>
+    </row>
+    <row r="33" spans="1:28">
+      <c r="A33" s="134"/>
+      <c r="B33" s="135"/>
+      <c r="C33" s="131"/>
+      <c r="D33" s="131"/>
+      <c r="E33" s="131"/>
+      <c r="F33" s="131"/>
+      <c r="G33" s="131"/>
+      <c r="H33" s="131"/>
+      <c r="I33" s="131"/>
+      <c r="J33" s="131"/>
+      <c r="K33" s="132"/>
+      <c r="L33" s="132"/>
+      <c r="M33" s="132"/>
+      <c r="N33" s="132"/>
+      <c r="O33" s="132"/>
+      <c r="P33" s="132"/>
+      <c r="Q33" s="132"/>
+      <c r="R33" s="132"/>
+      <c r="S33" s="132"/>
+      <c r="T33" s="132"/>
+      <c r="U33" s="132"/>
+      <c r="V33" s="132"/>
+      <c r="W33" s="132"/>
+      <c r="X33" s="132"/>
+      <c r="Y33" s="132"/>
+      <c r="Z33" s="132"/>
+      <c r="AA33" s="132"/>
+      <c r="AB33" s="132"/>
+    </row>
+    <row r="34" spans="1:28">
+      <c r="A34" s="136" t="s">
+        <v>327</v>
+      </c>
+      <c r="B34" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C34" s="137">
+        <v>5013000</v>
+      </c>
+      <c r="D34" s="137">
+        <v>4574400</v>
+      </c>
+      <c r="E34" s="137">
+        <v>4816800</v>
+      </c>
+      <c r="F34" s="137">
+        <v>4577700</v>
+      </c>
+      <c r="G34" s="137">
+        <v>5271500</v>
+      </c>
+      <c r="H34" s="137">
+        <v>5010600</v>
+      </c>
+      <c r="I34" s="137">
+        <v>5509600</v>
+      </c>
+      <c r="J34" s="137">
+        <v>6497600</v>
+      </c>
+      <c r="K34" s="137">
+        <v>6235300</v>
+      </c>
+      <c r="L34" s="137">
+        <v>6362600</v>
+      </c>
+      <c r="M34" s="137">
+        <v>6661700</v>
+      </c>
+      <c r="N34" s="137">
+        <v>7334500</v>
+      </c>
+      <c r="O34" s="137">
+        <v>7661700</v>
+      </c>
+      <c r="P34" s="137">
+        <v>7847200</v>
+      </c>
+      <c r="Q34" s="137">
+        <v>9019600</v>
+      </c>
+      <c r="R34" s="137">
+        <v>7812600</v>
+      </c>
+      <c r="S34" s="137">
+        <v>8500400</v>
+      </c>
+      <c r="T34" s="137">
+        <v>8856398</v>
+      </c>
+      <c r="U34" s="137">
+        <v>8675957</v>
+      </c>
+      <c r="V34" s="137">
+        <v>8477587</v>
+      </c>
+      <c r="W34" s="137">
+        <v>9115824</v>
+      </c>
+      <c r="X34" s="137">
+        <v>6422133</v>
+      </c>
+      <c r="Y34" s="137">
+        <v>5737514</v>
+      </c>
+      <c r="Z34" s="137">
+        <v>6471079</v>
+      </c>
+      <c r="AA34" s="93"/>
+      <c r="AB34" s="93"/>
+    </row>
+    <row r="35" spans="1:28">
+      <c r="A35" s="136" t="s">
+        <v>328</v>
+      </c>
+      <c r="B35" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C35" s="137"/>
+      <c r="D35" s="137"/>
+      <c r="E35" s="137"/>
+      <c r="F35" s="137"/>
+      <c r="G35" s="137"/>
+      <c r="H35" s="137"/>
+      <c r="I35" s="137"/>
+      <c r="J35" s="137"/>
+      <c r="K35" s="137"/>
+      <c r="L35" s="137"/>
+      <c r="M35" s="137"/>
+      <c r="N35" s="137"/>
+      <c r="O35" s="137"/>
+      <c r="P35" s="137"/>
+      <c r="Q35" s="137"/>
+      <c r="R35" s="137"/>
+      <c r="S35" s="137"/>
+      <c r="T35" s="137"/>
+      <c r="U35" s="137"/>
+      <c r="V35" s="137"/>
+      <c r="W35" s="137"/>
+      <c r="X35" s="137"/>
+      <c r="Y35" s="137">
+        <v>1223827</v>
+      </c>
+      <c r="Z35" s="137">
+        <v>1143776</v>
+      </c>
+      <c r="AA35" s="93"/>
+      <c r="AB35" s="93"/>
+    </row>
+    <row r="36" spans="1:28">
+      <c r="A36" s="136" t="s">
+        <v>329</v>
+      </c>
+      <c r="B36" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C36" s="137"/>
+      <c r="D36" s="137"/>
+      <c r="E36" s="137"/>
+      <c r="F36" s="137"/>
+      <c r="G36" s="137"/>
+      <c r="H36" s="137"/>
+      <c r="I36" s="137"/>
+      <c r="J36" s="137"/>
+      <c r="K36" s="137"/>
+      <c r="L36" s="137"/>
+      <c r="M36" s="137"/>
+      <c r="N36" s="137"/>
+      <c r="O36" s="137"/>
+      <c r="P36" s="137"/>
+      <c r="Q36" s="137"/>
+      <c r="R36" s="137"/>
+      <c r="S36" s="137"/>
+      <c r="T36" s="137"/>
+      <c r="U36" s="137"/>
+      <c r="V36" s="137"/>
+      <c r="W36" s="137"/>
+      <c r="X36" s="137"/>
+      <c r="Y36" s="137">
+        <v>372882</v>
+      </c>
+      <c r="Z36" s="137">
+        <v>361251</v>
+      </c>
+      <c r="AA36" s="93"/>
+      <c r="AB36" s="93"/>
+    </row>
+    <row r="37" spans="1:28">
+      <c r="A37" s="136" t="s">
+        <v>330</v>
+      </c>
+      <c r="B37" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C37" s="89"/>
+      <c r="D37" s="89"/>
+      <c r="E37" s="89"/>
+      <c r="F37" s="89"/>
+      <c r="G37" s="89"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="89"/>
+      <c r="J37" s="89"/>
+      <c r="K37" s="93"/>
+      <c r="L37" s="93"/>
+      <c r="M37" s="93"/>
+      <c r="N37" s="93"/>
+      <c r="O37" s="93"/>
+      <c r="P37" s="93"/>
+      <c r="Q37" s="93"/>
+      <c r="R37" s="138">
+        <f>R14</f>
+        <v>56825</v>
+      </c>
+      <c r="S37" s="138">
+        <f t="shared" ref="S37:U37" si="2">S14</f>
+        <v>46979</v>
+      </c>
+      <c r="T37" s="138">
+        <f t="shared" si="2"/>
+        <v>36295</v>
+      </c>
+      <c r="U37" s="138">
+        <f t="shared" si="2"/>
+        <v>189794</v>
+      </c>
+      <c r="V37" s="93"/>
+      <c r="W37" s="93"/>
+      <c r="X37" s="93"/>
+      <c r="Y37" s="137">
+        <v>206524</v>
+      </c>
+      <c r="Z37" s="137">
+        <v>110140</v>
+      </c>
+      <c r="AA37" s="93"/>
+      <c r="AB37" s="93"/>
+    </row>
+    <row r="38" spans="1:28">
+      <c r="A38" s="136" t="s">
+        <v>331</v>
+      </c>
+      <c r="B38" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C38" s="93"/>
+      <c r="D38" s="93"/>
+      <c r="E38" s="93"/>
+      <c r="F38" s="93"/>
+      <c r="G38" s="93"/>
+      <c r="H38" s="93"/>
+      <c r="I38" s="93"/>
+      <c r="J38" s="93"/>
+      <c r="K38" s="93"/>
+      <c r="L38" s="93"/>
+      <c r="M38" s="93"/>
+      <c r="N38" s="93"/>
+      <c r="O38" s="93"/>
+      <c r="P38" s="93"/>
+      <c r="Q38" s="93"/>
+      <c r="R38" s="93"/>
+      <c r="S38" s="93"/>
+      <c r="T38" s="93"/>
+      <c r="U38" s="93"/>
+      <c r="V38" s="93"/>
+      <c r="W38" s="93"/>
+      <c r="X38" s="93"/>
+      <c r="Y38" s="137">
+        <v>3934281</v>
+      </c>
+      <c r="Z38" s="137">
+        <v>4855912</v>
+      </c>
+      <c r="AA38" s="93"/>
+      <c r="AB38" s="93"/>
+    </row>
+    <row r="39" spans="1:28">
+      <c r="A39" s="136" t="s">
+        <v>332</v>
+      </c>
+      <c r="B39" s="88" t="s">
+        <v>295</v>
+      </c>
+      <c r="C39" s="89">
+        <v>1073420</v>
+      </c>
+      <c r="D39" s="89">
+        <v>703774</v>
+      </c>
+      <c r="E39" s="89">
+        <v>575934</v>
+      </c>
+      <c r="F39" s="89">
+        <v>264040</v>
+      </c>
+      <c r="G39" s="89">
+        <v>279516</v>
+      </c>
+      <c r="H39" s="89">
+        <v>328060</v>
+      </c>
+      <c r="I39" s="89">
+        <v>296056</v>
+      </c>
+      <c r="J39" s="89">
+        <v>290609</v>
+      </c>
+      <c r="K39" s="89">
+        <v>395861</v>
+      </c>
+      <c r="L39" s="89">
+        <v>543412</v>
+      </c>
+      <c r="M39" s="89">
+        <v>665598</v>
+      </c>
+      <c r="N39" s="89">
+        <v>788810</v>
+      </c>
+      <c r="O39" s="89">
+        <v>707499</v>
+      </c>
+      <c r="P39" s="89">
+        <v>758327</v>
+      </c>
+      <c r="Q39" s="89">
+        <v>687375</v>
+      </c>
+      <c r="R39" s="92">
+        <v>684752</v>
+      </c>
+      <c r="S39" s="92">
+        <v>718305</v>
+      </c>
+      <c r="T39" s="92">
+        <v>764190</v>
+      </c>
+      <c r="U39" s="92">
+        <v>846156</v>
+      </c>
+      <c r="V39" s="93"/>
+      <c r="W39" s="93"/>
+      <c r="X39" s="93"/>
+      <c r="Y39" s="93"/>
+      <c r="Z39" s="93"/>
+      <c r="AA39" s="93"/>
+      <c r="AB39" s="93"/>
+    </row>
+    <row r="40" spans="1:28" s="141" customFormat="1">
+      <c r="A40" s="139" t="s">
+        <v>333</v>
+      </c>
+      <c r="B40" s="140"/>
+      <c r="C40" s="131"/>
+      <c r="D40" s="131"/>
+      <c r="E40" s="131"/>
+      <c r="F40" s="131"/>
+      <c r="G40" s="131"/>
+      <c r="H40" s="131"/>
+      <c r="I40" s="131"/>
+      <c r="J40" s="131"/>
+      <c r="K40" s="132"/>
+      <c r="L40" s="132"/>
+      <c r="M40" s="132"/>
+      <c r="N40" s="132"/>
+      <c r="O40" s="132"/>
+      <c r="P40" s="132"/>
+      <c r="Q40" s="132"/>
+      <c r="R40" s="132"/>
+      <c r="S40" s="132"/>
+      <c r="T40" s="132"/>
+      <c r="U40" s="132"/>
+      <c r="V40" s="132"/>
+      <c r="W40" s="132"/>
+      <c r="X40" s="132"/>
+      <c r="Y40" s="132"/>
+      <c r="Z40" s="132"/>
+      <c r="AA40" s="132"/>
+      <c r="AB40" s="132"/>
+    </row>
+    <row r="41" spans="1:28">
+      <c r="A41" s="142" t="s">
+        <v>334</v>
+      </c>
+      <c r="B41" s="143" t="s">
+        <v>335</v>
+      </c>
+      <c r="C41" s="89">
+        <v>11825322</v>
+      </c>
+      <c r="D41" s="89">
+        <v>15955330</v>
+      </c>
+      <c r="E41" s="89">
+        <v>11746879</v>
+      </c>
+      <c r="F41" s="89">
+        <v>13879481</v>
+      </c>
+      <c r="G41" s="89">
+        <v>14778920</v>
+      </c>
+      <c r="H41" s="89">
+        <v>17327735</v>
+      </c>
+      <c r="I41" s="89">
+        <v>17637976</v>
+      </c>
+      <c r="J41" s="89">
+        <v>16263151</v>
+      </c>
+      <c r="K41" s="89">
+        <v>15042955</v>
+      </c>
+      <c r="L41" s="89">
+        <v>14878720</v>
+      </c>
+      <c r="M41" s="89">
+        <v>13011459</v>
+      </c>
+      <c r="N41" s="89">
+        <v>12800526</v>
+      </c>
+      <c r="O41" s="89">
+        <v>9396281</v>
+      </c>
+      <c r="P41" s="89">
+        <v>7751527</v>
+      </c>
+      <c r="Q41" s="89">
+        <v>6966646</v>
+      </c>
+      <c r="R41" s="93"/>
+      <c r="S41" s="93"/>
+      <c r="T41" s="93"/>
+      <c r="U41" s="93"/>
+      <c r="V41" s="93"/>
+      <c r="W41" s="93"/>
+      <c r="X41" s="93"/>
+      <c r="Y41" s="93"/>
+      <c r="Z41" s="93"/>
+      <c r="AA41" s="93"/>
+      <c r="AB41" s="93"/>
+    </row>
+    <row r="42" spans="1:28">
+      <c r="A42" s="142" t="s">
+        <v>336</v>
+      </c>
+      <c r="B42" s="143" t="s">
+        <v>295</v>
+      </c>
+      <c r="C42" s="89">
+        <v>7105272</v>
+      </c>
+      <c r="D42" s="89">
+        <v>7055335</v>
+      </c>
+      <c r="E42" s="89">
+        <v>6929253</v>
+      </c>
+      <c r="F42" s="89">
+        <v>7988515</v>
+      </c>
+      <c r="G42" s="89">
+        <v>8994905</v>
+      </c>
+      <c r="H42" s="89">
+        <v>9879241</v>
+      </c>
+      <c r="I42" s="89">
+        <v>9582760</v>
+      </c>
+      <c r="J42" s="89">
+        <v>9746176</v>
+      </c>
+      <c r="K42" s="89">
+        <v>9281807</v>
+      </c>
+      <c r="L42" s="89">
+        <v>9555999</v>
+      </c>
+      <c r="M42" s="89">
+        <v>7769016</v>
+      </c>
+      <c r="N42" s="89">
+        <v>7349667</v>
+      </c>
+      <c r="O42" s="89"/>
+      <c r="P42" s="89"/>
+      <c r="Q42" s="89"/>
+      <c r="R42" s="93"/>
+      <c r="S42" s="93"/>
+      <c r="T42" s="93"/>
+      <c r="U42" s="93"/>
+      <c r="V42" s="93"/>
+      <c r="W42" s="93"/>
+      <c r="X42" s="93"/>
+      <c r="Y42" s="93"/>
+      <c r="Z42" s="93"/>
+      <c r="AA42" s="93"/>
+      <c r="AB42" s="93"/>
+    </row>
+    <row r="43" spans="1:28">
+      <c r="A43" s="142" t="s">
+        <v>337</v>
+      </c>
+      <c r="B43" s="143" t="s">
+        <v>295</v>
+      </c>
+      <c r="C43" s="89">
+        <v>7528960</v>
+      </c>
+      <c r="D43" s="89">
+        <v>6672136</v>
+      </c>
+      <c r="E43" s="89">
+        <v>7351822</v>
+      </c>
+      <c r="F43" s="89">
+        <v>6825614</v>
+      </c>
+      <c r="G43" s="89">
+        <v>7712957</v>
+      </c>
+      <c r="H43" s="89">
+        <v>7827100</v>
+      </c>
+      <c r="I43" s="89">
+        <v>8353279</v>
+      </c>
+      <c r="J43" s="89">
+        <v>9790233</v>
+      </c>
+      <c r="K43" s="89">
+        <v>10442018</v>
+      </c>
+      <c r="L43" s="89">
+        <v>10607972</v>
+      </c>
+      <c r="M43" s="89">
+        <v>10486104</v>
+      </c>
+      <c r="N43" s="89">
+        <v>11322527</v>
+      </c>
+      <c r="O43" s="89">
+        <v>11875006</v>
+      </c>
+      <c r="P43" s="93"/>
+      <c r="Q43" s="93"/>
+      <c r="R43" s="93"/>
+      <c r="S43" s="93"/>
+      <c r="T43" s="93"/>
+      <c r="U43" s="93"/>
+      <c r="V43" s="93"/>
+      <c r="W43" s="93"/>
+      <c r="X43" s="93"/>
+      <c r="Y43" s="93"/>
+      <c r="Z43" s="93"/>
+      <c r="AA43" s="93"/>
+      <c r="AB43" s="93"/>
+    </row>
+    <row r="44" spans="1:28">
+      <c r="A44" s="142" t="s">
+        <v>338</v>
+      </c>
+      <c r="B44" s="143" t="s">
+        <v>295</v>
+      </c>
+      <c r="C44" s="89">
+        <v>5012999</v>
+      </c>
+      <c r="D44" s="89">
+        <v>4574378</v>
+      </c>
+      <c r="E44" s="89">
+        <v>4816840</v>
+      </c>
+      <c r="F44" s="89">
+        <v>4577709</v>
+      </c>
+      <c r="G44" s="89">
+        <v>5271530</v>
+      </c>
+      <c r="H44" s="89">
+        <v>5010578</v>
+      </c>
+      <c r="I44" s="89">
+        <v>5509647</v>
+      </c>
+      <c r="J44" s="89">
+        <v>6497589</v>
+      </c>
+      <c r="K44" s="89">
+        <v>6235347</v>
+      </c>
+      <c r="L44" s="89">
+        <v>6362619</v>
+      </c>
+      <c r="M44" s="89">
+        <v>6661746</v>
+      </c>
+      <c r="N44" s="89">
+        <v>7334450</v>
+      </c>
+      <c r="O44" s="89">
+        <v>7661686</v>
+      </c>
+      <c r="P44" s="89">
+        <v>7847187</v>
+      </c>
+      <c r="Q44" s="89">
+        <v>9019639</v>
+      </c>
+      <c r="R44" s="92">
+        <v>7812621</v>
+      </c>
+      <c r="S44" s="92">
+        <v>8500443</v>
+      </c>
+      <c r="T44" s="92">
+        <v>8856398</v>
+      </c>
+      <c r="U44" s="92">
+        <v>8675957</v>
+      </c>
+      <c r="V44" s="138">
+        <f>V34</f>
+        <v>8477587</v>
+      </c>
+      <c r="W44" s="138">
+        <f t="shared" ref="W44:Z44" si="3">W34</f>
+        <v>9115824</v>
+      </c>
+      <c r="X44" s="138">
+        <f t="shared" si="3"/>
+        <v>6422133</v>
+      </c>
+      <c r="Y44" s="138">
+        <f t="shared" si="3"/>
+        <v>5737514</v>
+      </c>
+      <c r="Z44" s="138">
+        <f t="shared" si="3"/>
+        <v>6471079</v>
+      </c>
+      <c r="AA44" s="93"/>
+      <c r="AB44" s="93"/>
+    </row>
+    <row r="45" spans="1:28">
+      <c r="A45" s="142" t="s">
+        <v>339</v>
+      </c>
+      <c r="B45" s="143" t="s">
+        <v>340</v>
+      </c>
+      <c r="C45" s="89">
+        <v>1206</v>
+      </c>
+      <c r="D45" s="89">
+        <v>880.44</v>
+      </c>
+      <c r="E45" s="89">
+        <v>939.31</v>
+      </c>
+      <c r="F45" s="89">
+        <v>851.08</v>
+      </c>
+      <c r="G45" s="89">
+        <v>1096.01</v>
+      </c>
+      <c r="H45" s="89">
+        <v>837.71</v>
+      </c>
+      <c r="I45" s="89">
+        <v>867.6</v>
+      </c>
+      <c r="J45" s="89">
+        <v>940.31</v>
+      </c>
+      <c r="K45" s="89">
+        <v>845.8682</v>
+      </c>
+      <c r="L45" s="89">
+        <v>752.15589999999997</v>
+      </c>
+      <c r="M45" s="89">
+        <v>876.46479999999997</v>
+      </c>
+      <c r="N45" s="89">
+        <v>740.08489999999995</v>
+      </c>
+      <c r="O45" s="89">
+        <v>771.44669999999996</v>
+      </c>
+      <c r="P45" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q45" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="R45" s="93"/>
+      <c r="S45" s="93"/>
+      <c r="T45" s="93"/>
+      <c r="U45" s="93"/>
+      <c r="V45" s="93"/>
+      <c r="W45" s="93"/>
+      <c r="X45" s="93"/>
+      <c r="Y45" s="93"/>
+      <c r="Z45" s="93"/>
+      <c r="AA45" s="93"/>
+      <c r="AB45" s="93"/>
+    </row>
+    <row r="46" spans="1:28">
+      <c r="A46" s="142" t="s">
+        <v>341</v>
+      </c>
+      <c r="B46" s="143" t="s">
+        <v>340</v>
+      </c>
+      <c r="C46" s="89">
+        <v>762</v>
+      </c>
+      <c r="D46" s="89">
+        <v>605.67999999999995</v>
+      </c>
+      <c r="E46" s="89">
+        <v>734.59</v>
+      </c>
+      <c r="F46" s="89">
+        <v>667.17</v>
+      </c>
+      <c r="G46" s="89">
+        <v>900.22</v>
+      </c>
+      <c r="H46" s="89">
+        <v>670.8</v>
+      </c>
+      <c r="I46" s="89">
+        <v>677.4</v>
+      </c>
+      <c r="J46" s="89">
+        <v>674.08</v>
+      </c>
+      <c r="K46" s="89">
+        <v>573.81610000000001</v>
+      </c>
+      <c r="L46" s="89">
+        <v>535.23979999999995</v>
+      </c>
+      <c r="M46" s="89">
+        <v>550.25559999999996</v>
+      </c>
+      <c r="N46" s="89">
+        <v>536.20339999999999</v>
+      </c>
+      <c r="O46" s="89">
+        <v>573.65250000000003</v>
+      </c>
+      <c r="P46" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q46" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="R46" s="93"/>
+      <c r="S46" s="93"/>
+      <c r="T46" s="93"/>
+      <c r="U46" s="93"/>
+      <c r="V46" s="93"/>
+      <c r="W46" s="93"/>
+      <c r="X46" s="93"/>
+      <c r="Y46" s="93"/>
+      <c r="Z46" s="93"/>
+      <c r="AA46" s="93"/>
+      <c r="AB46" s="93"/>
+    </row>
+    <row r="47" spans="1:28">
+      <c r="A47" s="144"/>
+      <c r="B47" s="145"/>
+      <c r="C47" s="146"/>
+      <c r="D47" s="146"/>
+      <c r="E47" s="146"/>
+      <c r="F47" s="146"/>
+      <c r="G47" s="146"/>
+      <c r="H47" s="146"/>
+      <c r="I47" s="146"/>
+      <c r="J47" s="146"/>
+      <c r="K47" s="146"/>
+      <c r="L47" s="146"/>
+      <c r="M47" s="146"/>
+      <c r="N47" s="146"/>
+      <c r="O47" s="146"/>
+      <c r="P47" s="146"/>
+      <c r="Q47" s="146"/>
+      <c r="R47" s="146"/>
+      <c r="S47" s="146"/>
+      <c r="T47" s="146"/>
+      <c r="U47" s="146"/>
+      <c r="V47" s="146"/>
+      <c r="W47" s="146"/>
+      <c r="X47" s="146"/>
+      <c r="Y47" s="146"/>
+      <c r="Z47" s="146"/>
+      <c r="AA47" s="146"/>
+      <c r="AB47" s="146"/>
+    </row>
+    <row r="48" spans="1:28">
+      <c r="A48" s="142" t="s">
+        <v>342</v>
+      </c>
+      <c r="B48" s="143" t="s">
+        <v>295</v>
+      </c>
+      <c r="C48" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="D48" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="E48" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="F48" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="G48" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="H48" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="I48" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="J48" s="89">
+        <v>504274</v>
+      </c>
+      <c r="K48" s="89">
+        <v>326754</v>
+      </c>
+      <c r="L48" s="89">
+        <v>463485</v>
+      </c>
+      <c r="M48" s="89">
+        <v>388021</v>
+      </c>
+      <c r="N48" s="89">
+        <v>416352</v>
+      </c>
+      <c r="O48" s="89">
+        <v>581520</v>
+      </c>
+      <c r="P48" s="89">
+        <v>688152</v>
+      </c>
+      <c r="Q48" s="89">
+        <v>602625</v>
+      </c>
+      <c r="R48" s="93"/>
+      <c r="S48" s="93"/>
+      <c r="T48" s="93"/>
+      <c r="U48" s="93"/>
+      <c r="V48" s="93"/>
+      <c r="W48" s="93"/>
+      <c r="X48" s="93"/>
+      <c r="Y48" s="93"/>
+      <c r="Z48" s="93"/>
+      <c r="AA48" s="93"/>
+      <c r="AB48" s="93"/>
+    </row>
+    <row r="49" spans="1:28">
+      <c r="A49" s="142" t="s">
+        <v>343</v>
+      </c>
+      <c r="B49" s="143" t="s">
+        <v>295</v>
+      </c>
+      <c r="C49" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="D49" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="E49" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="F49" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="G49" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="H49" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="I49" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="J49" s="89">
+        <v>115661</v>
+      </c>
+      <c r="K49" s="89">
+        <v>97472</v>
+      </c>
+      <c r="L49" s="89">
+        <v>137386</v>
+      </c>
+      <c r="M49" s="89">
+        <v>76355</v>
+      </c>
+      <c r="N49" s="89">
+        <v>119864</v>
+      </c>
+      <c r="O49" s="89">
+        <v>150484</v>
+      </c>
+      <c r="P49" s="89">
+        <v>169518</v>
+      </c>
+      <c r="Q49" s="89">
+        <v>135839</v>
+      </c>
+      <c r="R49" s="93"/>
+      <c r="S49" s="93"/>
+      <c r="T49" s="93"/>
+      <c r="U49" s="93"/>
+      <c r="V49" s="93"/>
+      <c r="W49" s="93"/>
+      <c r="X49" s="93"/>
+      <c r="Y49" s="93"/>
+      <c r="Z49" s="93"/>
+      <c r="AA49" s="93"/>
+      <c r="AB49" s="93"/>
+    </row>
+    <row r="50" spans="1:28">
+      <c r="A50" s="142" t="s">
+        <v>344</v>
+      </c>
+      <c r="B50" s="143" t="s">
+        <v>295</v>
+      </c>
+      <c r="C50" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="D50" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="E50" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="F50" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="G50" s="147">
+        <f>G25</f>
+        <v>805595</v>
+      </c>
+      <c r="H50" s="147">
+        <f t="shared" ref="H50:I50" si="4">H25</f>
+        <v>883723</v>
+      </c>
+      <c r="I50" s="147">
+        <f t="shared" si="4"/>
+        <v>350784</v>
+      </c>
+      <c r="J50" s="89">
+        <v>383591</v>
+      </c>
+      <c r="K50" s="89">
+        <v>229282</v>
+      </c>
+      <c r="L50" s="89">
+        <v>326099</v>
+      </c>
+      <c r="M50" s="89">
+        <v>311666</v>
+      </c>
+      <c r="N50" s="89">
+        <v>296488</v>
+      </c>
+      <c r="O50" s="89">
+        <v>431036</v>
+      </c>
+      <c r="P50" s="89">
+        <v>518634</v>
+      </c>
+      <c r="Q50" s="89">
+        <v>465187</v>
+      </c>
+      <c r="R50" s="138">
+        <f>R25</f>
+        <v>608803</v>
+      </c>
+      <c r="S50" s="138">
+        <f t="shared" ref="S50:W50" si="5">S25</f>
+        <v>554167</v>
+      </c>
+      <c r="T50" s="138">
+        <f t="shared" si="5"/>
+        <v>672428</v>
+      </c>
+      <c r="U50" s="138">
+        <f t="shared" si="5"/>
+        <v>750988</v>
+      </c>
+      <c r="V50" s="138">
+        <f t="shared" si="5"/>
+        <v>781476</v>
+      </c>
+      <c r="W50" s="138">
+        <f t="shared" si="5"/>
+        <v>680500</v>
+      </c>
+      <c r="X50" s="93"/>
+      <c r="Y50" s="93"/>
+      <c r="Z50" s="93"/>
+      <c r="AA50" s="93"/>
+      <c r="AB50" s="93"/>
+    </row>
+    <row r="51" spans="1:28">
+      <c r="A51" s="142" t="s">
+        <v>345</v>
+      </c>
+      <c r="B51" s="143" t="s">
+        <v>295</v>
+      </c>
+      <c r="C51" s="93"/>
+      <c r="D51" s="93"/>
+      <c r="E51" s="93"/>
+      <c r="F51" s="93"/>
+      <c r="G51" s="93"/>
+      <c r="H51" s="93"/>
+      <c r="I51" s="93"/>
+      <c r="J51" s="105">
+        <f>J10</f>
+        <v>5022</v>
+      </c>
+      <c r="K51" s="138">
+        <f>K48-K49-K50</f>
+        <v>0</v>
+      </c>
+      <c r="L51" s="138">
+        <f t="shared" ref="L51:P51" si="6">L48-L49-L50</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="138">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N51" s="138">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O51" s="138">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P51" s="138">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q51" s="138">
+        <f>Q10</f>
+        <v>1599</v>
+      </c>
+      <c r="R51" s="138">
+        <f>R10</f>
+        <v>666</v>
+      </c>
+      <c r="S51" s="138">
+        <f>S10</f>
+        <v>5931</v>
+      </c>
+      <c r="T51" s="138">
+        <f>T10</f>
+        <v>4266</v>
+      </c>
+      <c r="U51" s="138">
+        <f>U10</f>
+        <v>9522</v>
+      </c>
+      <c r="V51" s="93"/>
+      <c r="W51" s="93"/>
+      <c r="X51" s="93"/>
+      <c r="Y51" s="93"/>
+      <c r="Z51" s="93"/>
+      <c r="AA51" s="93"/>
+      <c r="AB51" s="93"/>
+    </row>
+    <row r="52" spans="1:28">
+      <c r="A52" s="144"/>
+      <c r="B52" s="145"/>
+      <c r="C52" s="146"/>
+      <c r="D52" s="146"/>
+      <c r="E52" s="146"/>
+      <c r="F52" s="146"/>
+      <c r="G52" s="146"/>
+      <c r="H52" s="146"/>
+      <c r="I52" s="146"/>
+      <c r="J52" s="146"/>
+      <c r="K52" s="146"/>
+      <c r="L52" s="146"/>
+      <c r="M52" s="146"/>
+      <c r="N52" s="146"/>
+      <c r="O52" s="146"/>
+      <c r="P52" s="146"/>
+      <c r="Q52" s="146"/>
+      <c r="R52" s="146"/>
+      <c r="S52" s="146"/>
+      <c r="T52" s="146"/>
+      <c r="U52" s="146"/>
+      <c r="V52" s="146"/>
+      <c r="W52" s="146"/>
+      <c r="X52" s="146"/>
+      <c r="Y52" s="146"/>
+      <c r="Z52" s="146"/>
+      <c r="AA52" s="146"/>
+      <c r="AB52" s="146"/>
+    </row>
+    <row r="53" spans="1:28">
+      <c r="A53" s="142" t="s">
+        <v>346</v>
+      </c>
+      <c r="B53" s="143"/>
+      <c r="C53" s="89">
+        <v>49977</v>
+      </c>
+      <c r="D53" s="89">
+        <v>134144</v>
+      </c>
+      <c r="E53" s="89">
+        <v>55560</v>
+      </c>
+      <c r="F53" s="89">
+        <v>58745</v>
+      </c>
+      <c r="G53" s="89">
+        <v>63424</v>
+      </c>
+      <c r="H53" s="89">
+        <v>68690</v>
+      </c>
+      <c r="I53" s="89">
+        <v>77537</v>
+      </c>
+      <c r="J53" s="89">
+        <v>69104</v>
+      </c>
+      <c r="K53" s="89">
+        <v>66571</v>
+      </c>
+      <c r="L53" s="89">
+        <v>61265</v>
+      </c>
+      <c r="M53" s="89">
+        <v>50866</v>
+      </c>
+      <c r="N53" s="89">
+        <v>56690</v>
+      </c>
+      <c r="O53" s="89">
+        <v>27831</v>
+      </c>
+      <c r="P53" s="89">
+        <v>26680</v>
+      </c>
+      <c r="Q53" s="89">
+        <v>31422</v>
+      </c>
+      <c r="R53" s="92">
+        <v>26441</v>
+      </c>
+      <c r="S53" s="92">
+        <v>31822</v>
+      </c>
+      <c r="T53" s="92">
+        <v>28763</v>
+      </c>
+      <c r="U53" s="92">
+        <v>30364</v>
+      </c>
+      <c r="V53" s="92">
+        <v>22767</v>
+      </c>
+      <c r="W53" s="93"/>
+      <c r="X53" s="93"/>
+      <c r="Y53" s="93"/>
+      <c r="Z53" s="93"/>
+      <c r="AA53" s="93"/>
+      <c r="AB53" s="93"/>
+    </row>
+    <row r="54" spans="1:28">
+      <c r="A54" s="142" t="s">
+        <v>347</v>
+      </c>
+      <c r="B54" s="143"/>
+      <c r="C54" s="89">
+        <v>278629</v>
+      </c>
+      <c r="D54" s="89">
+        <v>381095</v>
+      </c>
+      <c r="E54" s="89">
+        <v>487129</v>
+      </c>
+      <c r="F54" s="89">
+        <v>571263</v>
+      </c>
+      <c r="G54" s="89">
+        <v>558805</v>
+      </c>
+      <c r="H54" s="89">
+        <v>545191</v>
+      </c>
+      <c r="I54" s="89">
+        <v>577966</v>
+      </c>
+      <c r="J54" s="89">
+        <v>559244</v>
+      </c>
+      <c r="K54" s="89">
+        <v>591072</v>
+      </c>
+      <c r="L54" s="89">
+        <v>661796</v>
+      </c>
+      <c r="M54" s="89">
+        <v>660410</v>
+      </c>
+      <c r="N54" s="89">
+        <v>769168</v>
+      </c>
+      <c r="O54" s="89">
+        <v>915643</v>
+      </c>
+      <c r="P54" s="89">
+        <v>1071459</v>
+      </c>
+      <c r="Q54" s="89">
+        <v>1412326</v>
+      </c>
+      <c r="R54" s="92">
+        <v>1366950</v>
+      </c>
+      <c r="S54" s="92">
+        <v>1407419</v>
+      </c>
+      <c r="T54" s="92">
+        <v>1419171</v>
+      </c>
+      <c r="U54" s="92">
+        <v>1426929</v>
+      </c>
+      <c r="V54" s="92">
+        <v>1415566</v>
+      </c>
+      <c r="W54" s="93"/>
+      <c r="X54" s="93"/>
+      <c r="Y54" s="93"/>
+      <c r="Z54" s="93"/>
+      <c r="AA54" s="93"/>
+      <c r="AB54" s="93"/>
+    </row>
+    <row r="55" spans="1:28">
+      <c r="A55" s="142" t="s">
+        <v>348</v>
+      </c>
+      <c r="B55" s="143"/>
+      <c r="C55" s="89">
+        <v>185197</v>
+      </c>
+      <c r="D55" s="89">
+        <v>231605</v>
+      </c>
+      <c r="E55" s="89">
+        <v>278799</v>
+      </c>
+      <c r="F55" s="89">
+        <v>292462</v>
+      </c>
+      <c r="G55" s="89">
+        <v>230546</v>
+      </c>
+      <c r="H55" s="89">
+        <v>185892</v>
+      </c>
+      <c r="I55" s="89">
+        <v>161093</v>
+      </c>
+      <c r="J55" s="89">
+        <v>166001</v>
+      </c>
+      <c r="K55" s="89">
+        <v>185910</v>
+      </c>
+      <c r="L55" s="89">
+        <v>188748</v>
+      </c>
+      <c r="M55" s="89">
+        <v>196854</v>
+      </c>
+      <c r="N55" s="89">
+        <v>219512</v>
+      </c>
+      <c r="O55" s="89">
+        <v>272013</v>
+      </c>
+      <c r="P55" s="89">
+        <v>299639</v>
+      </c>
+      <c r="Q55" s="89">
+        <v>380891</v>
+      </c>
+      <c r="R55" s="92">
+        <v>81314</v>
+      </c>
+      <c r="S55" s="92">
+        <v>70415</v>
+      </c>
+      <c r="T55" s="92">
+        <v>72002</v>
+      </c>
+      <c r="U55" s="92">
+        <v>69911</v>
+      </c>
+      <c r="V55" s="93"/>
+      <c r="W55" s="93"/>
+      <c r="X55" s="93"/>
+      <c r="Y55" s="93"/>
+      <c r="Z55" s="93"/>
+      <c r="AA55" s="93"/>
+      <c r="AB55" s="93"/>
+    </row>
+    <row r="56" spans="1:28">
+      <c r="A56" s="142" t="s">
+        <v>349</v>
+      </c>
+      <c r="B56" s="143"/>
+      <c r="C56" s="89">
+        <v>2716983</v>
+      </c>
+      <c r="D56" s="89">
+        <v>3338239</v>
+      </c>
+      <c r="E56" s="89">
+        <v>3814565</v>
+      </c>
+      <c r="F56" s="89">
+        <v>4667463</v>
+      </c>
+      <c r="G56" s="89">
+        <v>4018174</v>
+      </c>
+      <c r="H56" s="89">
+        <v>2872799</v>
+      </c>
+      <c r="I56" s="89">
+        <v>2959595</v>
+      </c>
+      <c r="J56" s="89">
+        <v>2867516</v>
+      </c>
+      <c r="K56" s="89">
+        <v>3163081</v>
+      </c>
+      <c r="L56" s="89">
+        <v>3343846</v>
+      </c>
+      <c r="M56" s="89">
+        <v>4141786</v>
+      </c>
+      <c r="N56" s="89">
+        <v>5305505</v>
+      </c>
+      <c r="O56" s="89">
+        <v>5707761</v>
+      </c>
+      <c r="P56" s="89">
+        <v>6004062</v>
+      </c>
+      <c r="Q56" s="89">
+        <v>6777066</v>
+      </c>
+      <c r="R56" s="92">
+        <v>6713418</v>
+      </c>
+      <c r="S56" s="92">
+        <v>7043827</v>
+      </c>
+      <c r="T56" s="92">
+        <v>7021893</v>
+      </c>
+      <c r="U56" s="92">
+        <v>6463753</v>
+      </c>
+      <c r="V56" s="92">
+        <v>6320374</v>
+      </c>
+      <c r="W56" s="93"/>
+      <c r="X56" s="93"/>
+      <c r="Y56" s="93"/>
+      <c r="Z56" s="93"/>
+      <c r="AA56" s="93"/>
+      <c r="AB56" s="93"/>
+    </row>
+    <row r="57" spans="1:28">
+      <c r="A57" s="142" t="s">
+        <v>350</v>
+      </c>
+      <c r="B57" s="143"/>
+      <c r="C57" s="89"/>
+      <c r="D57" s="89"/>
+      <c r="E57" s="89"/>
+      <c r="F57" s="89"/>
+      <c r="G57" s="89"/>
+      <c r="H57" s="89"/>
+      <c r="I57" s="89"/>
+      <c r="J57" s="89"/>
+      <c r="K57" s="93"/>
+      <c r="L57" s="93"/>
+      <c r="M57" s="93"/>
+      <c r="N57" s="93"/>
+      <c r="O57" s="93"/>
+      <c r="P57" s="93"/>
+      <c r="Q57" s="93"/>
+      <c r="R57" s="93"/>
+      <c r="S57" s="93"/>
+      <c r="T57" s="93"/>
+      <c r="U57" s="93"/>
+      <c r="V57" s="93"/>
+      <c r="W57" s="93"/>
+      <c r="X57" s="93"/>
+      <c r="Y57" s="93"/>
+      <c r="Z57" s="93"/>
+      <c r="AA57" s="93"/>
+      <c r="AB57" s="93"/>
+    </row>
+    <row r="58" spans="1:28">
+      <c r="A58" s="142" t="s">
+        <v>351</v>
+      </c>
+      <c r="B58" s="143"/>
+      <c r="C58" s="89">
+        <v>279455</v>
+      </c>
+      <c r="D58" s="89">
+        <v>330217</v>
+      </c>
+      <c r="E58" s="89">
+        <v>371240</v>
+      </c>
+      <c r="F58" s="89">
+        <v>329505</v>
+      </c>
+      <c r="G58" s="89">
+        <v>309582</v>
+      </c>
+      <c r="H58" s="89">
+        <v>343755</v>
+      </c>
+      <c r="I58" s="89">
+        <v>400296</v>
+      </c>
+      <c r="J58" s="89">
+        <v>304676</v>
+      </c>
+      <c r="K58" s="93"/>
+      <c r="L58" s="93"/>
+      <c r="M58" s="93"/>
+      <c r="N58" s="93"/>
+      <c r="O58" s="93"/>
+      <c r="P58" s="93"/>
+      <c r="Q58" s="93"/>
+      <c r="R58" s="93"/>
+      <c r="S58" s="93"/>
+      <c r="T58" s="93"/>
+      <c r="U58" s="93"/>
+      <c r="V58" s="93"/>
+      <c r="W58" s="93"/>
+      <c r="X58" s="93"/>
+      <c r="Y58" s="93"/>
+      <c r="Z58" s="93"/>
+      <c r="AA58" s="93"/>
+      <c r="AB58" s="93"/>
+    </row>
+    <row r="59" spans="1:28">
+      <c r="A59" s="142" t="s">
+        <v>352</v>
+      </c>
+      <c r="B59" s="143"/>
+      <c r="C59" s="89">
+        <v>47494</v>
+      </c>
+      <c r="D59" s="89">
+        <v>85619</v>
+      </c>
+      <c r="E59" s="89">
+        <v>79097</v>
+      </c>
+      <c r="F59" s="89">
+        <v>94099</v>
+      </c>
+      <c r="G59" s="89">
+        <v>99196</v>
+      </c>
+      <c r="H59" s="89">
+        <v>98291</v>
+      </c>
+      <c r="I59" s="89">
+        <v>97605</v>
+      </c>
+      <c r="J59" s="89">
+        <v>79571</v>
+      </c>
+      <c r="K59" s="93"/>
+      <c r="L59" s="93"/>
+      <c r="M59" s="93"/>
+      <c r="N59" s="93"/>
+      <c r="O59" s="93"/>
+      <c r="P59" s="93"/>
+      <c r="Q59" s="93"/>
+      <c r="R59" s="93"/>
+      <c r="S59" s="93"/>
+      <c r="T59" s="93"/>
+      <c r="U59" s="93"/>
+      <c r="V59" s="93"/>
+      <c r="W59" s="93"/>
+      <c r="X59" s="93"/>
+      <c r="Y59" s="93"/>
+      <c r="Z59" s="93"/>
+      <c r="AA59" s="93"/>
+      <c r="AB59" s="93"/>
+    </row>
+    <row r="60" spans="1:28">
+      <c r="A60" s="142" t="s">
+        <v>353</v>
+      </c>
+      <c r="B60" s="143"/>
+      <c r="C60" s="89"/>
+      <c r="D60" s="89"/>
+      <c r="E60" s="89"/>
+      <c r="F60" s="89"/>
+      <c r="G60" s="89"/>
+      <c r="H60" s="89"/>
+      <c r="I60" s="89"/>
+      <c r="J60" s="89"/>
+      <c r="K60" s="93"/>
+      <c r="L60" s="93"/>
+      <c r="M60" s="93"/>
+      <c r="N60" s="93"/>
+      <c r="O60" s="93"/>
+      <c r="P60" s="93"/>
+      <c r="Q60" s="93"/>
+      <c r="R60" s="93"/>
+      <c r="S60" s="93"/>
+      <c r="T60" s="93"/>
+      <c r="U60" s="93"/>
+      <c r="V60" s="93"/>
+      <c r="W60" s="93"/>
+      <c r="X60" s="93"/>
+      <c r="Y60" s="93"/>
+      <c r="Z60" s="93"/>
+      <c r="AA60" s="93"/>
+      <c r="AB60" s="93"/>
+    </row>
+    <row r="61" spans="1:28" ht="28.5">
+      <c r="A61" s="142" t="s">
+        <v>354</v>
+      </c>
+      <c r="B61" s="143"/>
+      <c r="C61" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="D61" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="E61" s="89">
+        <v>213725</v>
+      </c>
+      <c r="F61" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="G61" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="H61" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="I61" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="J61" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="K61" s="93"/>
+      <c r="L61" s="93"/>
+      <c r="M61" s="93"/>
+      <c r="N61" s="93"/>
+      <c r="O61" s="93"/>
+      <c r="P61" s="93"/>
+      <c r="Q61" s="93"/>
+      <c r="R61" s="93"/>
+      <c r="S61" s="93"/>
+      <c r="T61" s="93"/>
+      <c r="U61" s="93"/>
+      <c r="V61" s="93"/>
+      <c r="W61" s="93"/>
+      <c r="X61" s="93"/>
+      <c r="Y61" s="93"/>
+      <c r="Z61" s="93"/>
+      <c r="AA61" s="93"/>
+      <c r="AB61" s="93"/>
+    </row>
+    <row r="62" spans="1:28">
+      <c r="A62" s="142" t="s">
+        <v>355</v>
+      </c>
+      <c r="B62" s="143"/>
+      <c r="C62" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="D62" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="E62" s="89">
+        <v>67991</v>
+      </c>
+      <c r="F62" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="G62" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="H62" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="I62" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="J62" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="K62" s="93"/>
+      <c r="L62" s="93"/>
+      <c r="M62" s="93"/>
+      <c r="N62" s="93"/>
+      <c r="O62" s="93"/>
+      <c r="P62" s="93"/>
+      <c r="Q62" s="93"/>
+      <c r="R62" s="93"/>
+      <c r="S62" s="93"/>
+      <c r="T62" s="93"/>
+      <c r="U62" s="93"/>
+      <c r="V62" s="93"/>
+      <c r="W62" s="93"/>
+      <c r="X62" s="93"/>
+      <c r="Y62" s="93"/>
+      <c r="Z62" s="93"/>
+      <c r="AA62" s="93"/>
+      <c r="AB62" s="93"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="17" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A603B2BF-F20E-4944-9345-8CBE4565034E}">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="9" style="63"/>
-    <col min="3" max="14" width="10.875" style="63" customWidth="1"/>
-    <col min="15" max="15" width="11.625" style="55" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="55"/>
+    <col min="3" max="15" width="10.875" style="63" customWidth="1"/>
+    <col min="16" max="16" width="11.625" style="55" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14.25" customHeight="1">
-      <c r="A1" s="97" t="s">
+    <row r="1" spans="1:17" ht="14.25" customHeight="1">
+      <c r="A1" s="165" t="s">
         <v>265</v>
       </c>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="165" t="s">
         <v>264</v>
       </c>
-      <c r="C1" s="86" t="s">
+      <c r="C1" s="154" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="90" t="s">
+      <c r="D1" s="158" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="86" t="s">
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="154" t="s">
         <v>263</v>
       </c>
-      <c r="M1" s="86"/>
-      <c r="N1" s="86"/>
-      <c r="O1" s="76" t="s">
+      <c r="N1" s="154"/>
+      <c r="O1" s="154"/>
+      <c r="P1" s="75" t="s">
         <v>266</v>
       </c>
-      <c r="P1" s="55" t="s">
+      <c r="Q1" s="55" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="72">
-      <c r="A2" s="98"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="87"/>
+    <row r="2" spans="1:17" ht="72">
+      <c r="A2" s="166"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="155"/>
       <c r="D2" s="8" t="s">
         <v>105</v>
       </c>
@@ -9235,705 +14546,744 @@
       <c r="H2" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="J2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="K2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="L2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="M2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="N2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="O2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="P2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="75" t="s">
+      <c r="Q2" s="74" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="A3" s="68" t="s">
         <v>255</v>
       </c>
       <c r="B3" s="67">
         <v>2015</v>
       </c>
-      <c r="C3" s="74">
+      <c r="C3" s="73">
         <v>7683695</v>
       </c>
-      <c r="D3" s="74">
-        <v>4362589</v>
-      </c>
-      <c r="E3" s="74">
+      <c r="D3" s="73" cm="1">
+        <f t="array" ref="D3:D13">TRANSPOSE('Forestry Statistics'!$R$4:$AB$4)</f>
+        <v>4361827</v>
+      </c>
+      <c r="E3" s="73" cm="1">
+        <f t="array" ref="E3:E13">TRANSPOSE('Forestry Statistics'!$R$8:$AB$8)</f>
         <v>128390</v>
       </c>
-      <c r="F3" s="74">
+      <c r="F3" s="73" cm="1">
+        <f t="array" ref="F3:F13">TRANSPOSE('Forestry Statistics'!R23:AB23)</f>
         <v>2152877</v>
       </c>
-      <c r="G3" s="74">
+      <c r="G3" s="73" cm="1">
+        <f t="array" ref="G3:G13">TRANSPOSE('Forestry Statistics'!R15:AB15)</f>
         <v>739334</v>
       </c>
-      <c r="H3" s="74">
-        <v>300505</v>
-      </c>
-      <c r="I3" s="72">
-        <f t="shared" ref="I3:I13" si="0">D3+E3+H3</f>
-        <v>4791484</v>
-      </c>
-      <c r="J3" s="72">
-        <f t="shared" ref="J3:J13" si="1">F3</f>
-        <v>2152877</v>
-      </c>
-      <c r="K3" s="72">
-        <f t="shared" ref="K3:K13" si="2">G3</f>
-        <v>739334</v>
-      </c>
-      <c r="L3" s="72">
-        <f t="shared" ref="L3:L13" si="3">ROUND(I3*2.47,0)</f>
-        <v>11834965</v>
-      </c>
-      <c r="M3" s="77">
-        <f t="shared" ref="M3:M13" si="4">ROUND(J3*2.47,0)</f>
-        <v>5317606</v>
-      </c>
-      <c r="N3" s="72">
-        <f t="shared" ref="N3:N13" si="5">ROUND(K3*2.47,0)</f>
-        <v>1826155</v>
-      </c>
-      <c r="O3" s="80"/>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="H3" s="73" cm="1">
+        <f t="array" ref="H3:H13">TRANSPOSE('Forestry Statistics'!R11:AB11)</f>
+        <v>299577</v>
+      </c>
+      <c r="I3" s="73" cm="1">
+        <f t="array" ref="I3:I13">TRANSPOSE('Forestry Statistics'!R34:AB34)</f>
+        <v>7812600</v>
+      </c>
+      <c r="J3" s="71">
+        <f>D3+E3+H3</f>
+        <v>4789794</v>
+      </c>
+      <c r="K3" s="71">
+        <f>I3</f>
+        <v>7812600</v>
+      </c>
+      <c r="L3" s="71">
+        <f>G3+F3</f>
+        <v>2892211</v>
+      </c>
+      <c r="M3" s="71">
+        <f t="shared" ref="M3:M13" si="0">ROUND(J3*2.47,0)</f>
+        <v>11830791</v>
+      </c>
+      <c r="N3" s="76">
+        <f>ROUND(K3*2.47,0)</f>
+        <v>19297122</v>
+      </c>
+      <c r="O3" s="71">
+        <f t="shared" ref="O3:O13" si="1">ROUND(L3*2.47,0)</f>
+        <v>7143761</v>
+      </c>
+      <c r="P3" s="79"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="68" t="s">
         <v>255</v>
       </c>
       <c r="B4" s="67">
         <v>2016</v>
       </c>
-      <c r="C4" s="74">
+      <c r="C4" s="73">
         <v>7203509</v>
       </c>
-      <c r="D4" s="74">
+      <c r="D4" s="73">
         <v>3823656</v>
       </c>
-      <c r="E4" s="74">
+      <c r="E4" s="73">
         <v>162322</v>
       </c>
-      <c r="F4" s="74">
+      <c r="F4" s="73">
         <v>1953638</v>
       </c>
-      <c r="G4" s="74">
+      <c r="G4" s="73">
         <v>991088</v>
       </c>
-      <c r="H4" s="74">
+      <c r="H4" s="73">
         <v>272805</v>
       </c>
-      <c r="I4" s="72">
-        <f t="shared" si="0"/>
+      <c r="I4" s="73">
+        <v>8500400</v>
+      </c>
+      <c r="J4" s="71">
+        <f t="shared" ref="J4:J13" si="2">D4+E4+H4</f>
         <v>4258783</v>
       </c>
-      <c r="J4" s="72">
+      <c r="K4" s="71">
+        <f t="shared" ref="K4:K13" si="3">I4</f>
+        <v>8500400</v>
+      </c>
+      <c r="L4" s="71">
+        <f t="shared" ref="L4:L13" si="4">G4+F4</f>
+        <v>2944726</v>
+      </c>
+      <c r="M4" s="71">
+        <f t="shared" si="0"/>
+        <v>10519194</v>
+      </c>
+      <c r="N4" s="76">
+        <f t="shared" ref="N3:N13" si="5">ROUND(K4*2.47,0)</f>
+        <v>20995988</v>
+      </c>
+      <c r="O4" s="71">
         <f t="shared" si="1"/>
-        <v>1953638</v>
-      </c>
-      <c r="K4" s="72">
-        <f t="shared" si="2"/>
-        <v>991088</v>
-      </c>
-      <c r="L4" s="72">
-        <f t="shared" si="3"/>
-        <v>10519194</v>
-      </c>
-      <c r="M4" s="77">
-        <f t="shared" si="4"/>
-        <v>4825486</v>
-      </c>
-      <c r="N4" s="72">
-        <f t="shared" si="5"/>
-        <v>2447987</v>
-      </c>
-      <c r="O4" s="80"/>
-    </row>
-    <row r="5" spans="1:16">
+        <v>7273473</v>
+      </c>
+      <c r="P4" s="79"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="68" t="s">
         <v>255</v>
       </c>
       <c r="B5" s="67">
         <v>2017</v>
       </c>
-      <c r="C5" s="74">
+      <c r="C5" s="73">
         <v>7680711</v>
       </c>
-      <c r="D5" s="74">
+      <c r="D5" s="73">
         <v>4295890</v>
       </c>
-      <c r="E5" s="74">
+      <c r="E5" s="73">
         <v>141220</v>
       </c>
-      <c r="F5" s="74">
+      <c r="F5" s="73">
         <v>1657169</v>
       </c>
-      <c r="G5" s="74">
+      <c r="G5" s="73">
         <v>1280993</v>
       </c>
-      <c r="H5" s="74">
+      <c r="H5" s="73">
         <v>305439</v>
       </c>
-      <c r="I5" s="72">
-        <f t="shared" si="0"/>
+      <c r="I5" s="73">
+        <v>8856398</v>
+      </c>
+      <c r="J5" s="71">
+        <f t="shared" si="2"/>
         <v>4742549</v>
       </c>
-      <c r="J5" s="72">
+      <c r="K5" s="71">
+        <f t="shared" si="3"/>
+        <v>8856398</v>
+      </c>
+      <c r="L5" s="71">
+        <f t="shared" si="4"/>
+        <v>2938162</v>
+      </c>
+      <c r="M5" s="71">
+        <f t="shared" si="0"/>
+        <v>11714096</v>
+      </c>
+      <c r="N5" s="76">
+        <f t="shared" si="5"/>
+        <v>21875303</v>
+      </c>
+      <c r="O5" s="71">
         <f t="shared" si="1"/>
-        <v>1657169</v>
-      </c>
-      <c r="K5" s="72">
-        <f t="shared" si="2"/>
-        <v>1280993</v>
-      </c>
-      <c r="L5" s="72">
-        <f t="shared" si="3"/>
-        <v>11714096</v>
-      </c>
-      <c r="M5" s="77">
-        <f t="shared" si="4"/>
-        <v>4093207</v>
-      </c>
-      <c r="N5" s="72">
-        <f t="shared" si="5"/>
-        <v>3164053</v>
-      </c>
-      <c r="O5" s="80"/>
-    </row>
-    <row r="6" spans="1:16">
+        <v>7257260</v>
+      </c>
+      <c r="P5" s="79"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="68" t="s">
         <v>255</v>
       </c>
       <c r="B6" s="67">
         <v>2018</v>
       </c>
-      <c r="C6" s="74">
+      <c r="C6" s="73">
         <v>7299473</v>
       </c>
-      <c r="D6" s="74">
+      <c r="D6" s="73">
         <v>3677952</v>
       </c>
-      <c r="E6" s="74">
+      <c r="E6" s="73">
         <v>135429</v>
       </c>
-      <c r="F6" s="74">
+      <c r="F6" s="73">
         <v>1785067</v>
       </c>
-      <c r="G6" s="74">
+      <c r="G6" s="73">
         <v>1329166</v>
       </c>
-      <c r="H6" s="74">
+      <c r="H6" s="73">
         <v>371859</v>
       </c>
-      <c r="I6" s="72">
-        <f t="shared" si="0"/>
+      <c r="I6" s="73">
+        <v>8675957</v>
+      </c>
+      <c r="J6" s="71">
+        <f t="shared" si="2"/>
         <v>4185240</v>
       </c>
-      <c r="J6" s="72">
+      <c r="K6" s="71">
+        <f t="shared" si="3"/>
+        <v>8675957</v>
+      </c>
+      <c r="L6" s="71">
+        <f t="shared" si="4"/>
+        <v>3114233</v>
+      </c>
+      <c r="M6" s="71">
+        <f t="shared" si="0"/>
+        <v>10337543</v>
+      </c>
+      <c r="N6" s="76">
+        <f t="shared" si="5"/>
+        <v>21429614</v>
+      </c>
+      <c r="O6" s="71">
         <f t="shared" si="1"/>
-        <v>1785067</v>
-      </c>
-      <c r="K6" s="72">
-        <f t="shared" si="2"/>
-        <v>1329166</v>
-      </c>
-      <c r="L6" s="72">
-        <f t="shared" si="3"/>
-        <v>10337543</v>
-      </c>
-      <c r="M6" s="77">
-        <f t="shared" si="4"/>
-        <v>4409115</v>
-      </c>
-      <c r="N6" s="72">
-        <f t="shared" si="5"/>
-        <v>3283040</v>
-      </c>
-      <c r="O6" s="80"/>
-    </row>
-    <row r="7" spans="1:16">
+        <v>7692156</v>
+      </c>
+      <c r="P6" s="79"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="68" t="s">
         <v>242</v>
       </c>
       <c r="B7" s="67">
         <v>2019</v>
       </c>
-      <c r="C7" s="74">
+      <c r="C7" s="73">
         <v>7390294</v>
       </c>
-      <c r="D7" s="74">
+      <c r="D7" s="73">
         <v>3458315</v>
       </c>
-      <c r="E7" s="74">
+      <c r="E7" s="73">
         <v>125565</v>
       </c>
-      <c r="F7" s="74">
+      <c r="F7" s="73">
         <v>1898314</v>
       </c>
-      <c r="G7" s="74">
+      <c r="G7" s="73">
         <v>1537877</v>
       </c>
-      <c r="H7" s="74">
+      <c r="H7" s="73">
         <v>370223</v>
       </c>
-      <c r="I7" s="72">
-        <f t="shared" si="0"/>
+      <c r="I7" s="73">
+        <v>8477587</v>
+      </c>
+      <c r="J7" s="71">
+        <f t="shared" si="2"/>
         <v>3954103</v>
       </c>
-      <c r="J7" s="72">
+      <c r="K7" s="71">
+        <f t="shared" si="3"/>
+        <v>8477587</v>
+      </c>
+      <c r="L7" s="71">
+        <f t="shared" si="4"/>
+        <v>3436191</v>
+      </c>
+      <c r="M7" s="71">
+        <f t="shared" si="0"/>
+        <v>9766634</v>
+      </c>
+      <c r="N7" s="76">
+        <f t="shared" si="5"/>
+        <v>20939640</v>
+      </c>
+      <c r="O7" s="71">
         <f t="shared" si="1"/>
-        <v>1898314</v>
-      </c>
-      <c r="K7" s="72">
-        <f t="shared" si="2"/>
-        <v>1537877</v>
-      </c>
-      <c r="L7" s="72">
-        <f t="shared" si="3"/>
-        <v>9766634</v>
-      </c>
-      <c r="M7" s="77">
-        <f t="shared" si="4"/>
-        <v>4688836</v>
-      </c>
-      <c r="N7" s="72">
-        <f t="shared" si="5"/>
-        <v>3798556</v>
-      </c>
-      <c r="O7" s="80"/>
-    </row>
-    <row r="8" spans="1:16">
+        <v>8487392</v>
+      </c>
+      <c r="P7" s="79"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="68" t="s">
         <v>255</v>
       </c>
       <c r="B8" s="67">
         <v>2020</v>
       </c>
-      <c r="C8" s="74">
+      <c r="C8" s="73">
         <v>6933696</v>
       </c>
-      <c r="D8" s="74">
+      <c r="D8" s="73">
         <v>3000060</v>
       </c>
-      <c r="E8" s="74">
+      <c r="E8" s="73">
         <v>151496</v>
       </c>
-      <c r="F8" s="74">
+      <c r="F8" s="73">
         <v>1774608</v>
       </c>
-      <c r="G8" s="74">
+      <c r="G8" s="73">
         <v>1619648</v>
       </c>
-      <c r="H8" s="74">
+      <c r="H8" s="73">
         <v>387884</v>
       </c>
-      <c r="I8" s="72">
-        <f t="shared" si="0"/>
+      <c r="I8" s="73">
+        <v>9115824</v>
+      </c>
+      <c r="J8" s="71">
+        <f t="shared" si="2"/>
         <v>3539440</v>
       </c>
-      <c r="J8" s="72">
+      <c r="K8" s="71">
+        <f t="shared" si="3"/>
+        <v>9115824</v>
+      </c>
+      <c r="L8" s="71">
+        <f t="shared" si="4"/>
+        <v>3394256</v>
+      </c>
+      <c r="M8" s="71">
+        <f t="shared" si="0"/>
+        <v>8742417</v>
+      </c>
+      <c r="N8" s="76">
+        <f t="shared" si="5"/>
+        <v>22516085</v>
+      </c>
+      <c r="O8" s="71">
         <f t="shared" si="1"/>
-        <v>1774608</v>
-      </c>
-      <c r="K8" s="72">
-        <f t="shared" si="2"/>
-        <v>1619648</v>
-      </c>
-      <c r="L8" s="72">
-        <f t="shared" si="3"/>
-        <v>8742417</v>
-      </c>
-      <c r="M8" s="77">
-        <f t="shared" si="4"/>
-        <v>4383282</v>
-      </c>
-      <c r="N8" s="72">
-        <f t="shared" si="5"/>
-        <v>4000531</v>
-      </c>
-      <c r="O8" s="77">
-        <f>M8</f>
-        <v>4383282</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>8383812</v>
+      </c>
+      <c r="P8" s="76">
+        <f>N8</f>
+        <v>22516085</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="68" t="s">
         <v>255</v>
       </c>
       <c r="B9" s="67">
         <v>2021</v>
       </c>
-      <c r="C9" s="74">
+      <c r="C9" s="73">
         <v>3754373</v>
       </c>
-      <c r="D9" s="74">
+      <c r="D9" s="73">
         <v>1085095</v>
       </c>
-      <c r="E9" s="74">
+      <c r="E9" s="73">
         <v>172239</v>
       </c>
-      <c r="F9" s="74">
+      <c r="F9" s="73">
         <v>1235098</v>
       </c>
-      <c r="G9" s="74">
+      <c r="G9" s="73">
         <v>1011349</v>
       </c>
-      <c r="H9" s="74">
+      <c r="H9" s="73">
         <v>250593</v>
       </c>
-      <c r="I9" s="72">
-        <f t="shared" si="0"/>
+      <c r="I9" s="73">
+        <v>6422133</v>
+      </c>
+      <c r="J9" s="71">
+        <f t="shared" si="2"/>
         <v>1507927</v>
       </c>
-      <c r="J9" s="72">
+      <c r="K9" s="71">
+        <f t="shared" si="3"/>
+        <v>6422133</v>
+      </c>
+      <c r="L9" s="71">
+        <f t="shared" si="4"/>
+        <v>2246447</v>
+      </c>
+      <c r="M9" s="71">
+        <f t="shared" si="0"/>
+        <v>3724580</v>
+      </c>
+      <c r="N9" s="76">
+        <f t="shared" si="5"/>
+        <v>15862669</v>
+      </c>
+      <c r="O9" s="71">
         <f t="shared" si="1"/>
-        <v>1235098</v>
-      </c>
-      <c r="K9" s="72">
-        <f t="shared" si="2"/>
-        <v>1011349</v>
-      </c>
-      <c r="L9" s="72">
-        <f t="shared" si="3"/>
-        <v>3724580</v>
-      </c>
-      <c r="M9" s="77">
-        <f t="shared" si="4"/>
-        <v>3050692</v>
-      </c>
-      <c r="N9" s="72">
-        <f t="shared" si="5"/>
-        <v>2498032</v>
-      </c>
-      <c r="O9" s="77">
-        <f>M9+O8</f>
-        <v>7433974</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>5548724</v>
+      </c>
+      <c r="P9" s="76">
+        <f>N9+P8</f>
+        <v>38378754</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="68" t="s">
         <v>255</v>
       </c>
       <c r="B10" s="67">
         <v>2022</v>
       </c>
-      <c r="C10" s="74">
+      <c r="C10" s="73">
         <v>4202790</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="73">
         <v>930860</v>
       </c>
-      <c r="E10" s="74">
+      <c r="E10" s="73">
         <v>166099</v>
       </c>
-      <c r="F10" s="74">
+      <c r="F10" s="73">
         <v>1057316</v>
       </c>
-      <c r="G10" s="74">
+      <c r="G10" s="73">
         <v>1582935</v>
       </c>
-      <c r="H10" s="74">
+      <c r="H10" s="73">
         <v>465579</v>
       </c>
-      <c r="I10" s="72">
-        <f t="shared" si="0"/>
+      <c r="I10" s="73">
+        <v>5737514</v>
+      </c>
+      <c r="J10" s="71">
+        <f t="shared" si="2"/>
         <v>1562538</v>
       </c>
-      <c r="J10" s="72">
+      <c r="K10" s="71">
+        <f t="shared" si="3"/>
+        <v>5737514</v>
+      </c>
+      <c r="L10" s="71">
+        <f t="shared" si="4"/>
+        <v>2640251</v>
+      </c>
+      <c r="M10" s="71">
+        <f t="shared" si="0"/>
+        <v>3859469</v>
+      </c>
+      <c r="N10" s="76">
+        <f t="shared" si="5"/>
+        <v>14171660</v>
+      </c>
+      <c r="O10" s="71">
         <f t="shared" si="1"/>
-        <v>1057316</v>
-      </c>
-      <c r="K10" s="72">
-        <f t="shared" si="2"/>
-        <v>1582935</v>
-      </c>
-      <c r="L10" s="72">
-        <f t="shared" si="3"/>
-        <v>3859469</v>
-      </c>
-      <c r="M10" s="77">
-        <f t="shared" si="4"/>
-        <v>2611571</v>
-      </c>
-      <c r="N10" s="72">
-        <f t="shared" si="5"/>
-        <v>3909849</v>
-      </c>
-      <c r="O10" s="77">
-        <f t="shared" ref="O10:O13" si="6">M10+O9</f>
-        <v>10045545</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>6521420</v>
+      </c>
+      <c r="P10" s="76">
+        <f t="shared" ref="P10:P13" si="6">N10+P9</f>
+        <v>52550414</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="68" t="s">
         <v>255</v>
       </c>
       <c r="B11" s="67">
         <v>2023</v>
       </c>
-      <c r="C11" s="74">
+      <c r="C11" s="73">
         <v>4636119</v>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="73">
         <v>1014361</v>
       </c>
-      <c r="E11" s="74">
+      <c r="E11" s="73">
         <v>66997</v>
       </c>
-      <c r="F11" s="74">
+      <c r="F11" s="73">
         <v>1133101</v>
       </c>
-      <c r="G11" s="74">
+      <c r="G11" s="73">
         <v>1795750</v>
       </c>
-      <c r="H11" s="74">
+      <c r="H11" s="73">
         <v>625911</v>
       </c>
-      <c r="I11" s="72">
-        <f t="shared" si="0"/>
+      <c r="I11" s="73">
+        <v>6471079</v>
+      </c>
+      <c r="J11" s="71">
+        <f t="shared" si="2"/>
         <v>1707269</v>
       </c>
-      <c r="J11" s="72">
+      <c r="K11" s="71">
+        <f t="shared" si="3"/>
+        <v>6471079</v>
+      </c>
+      <c r="L11" s="71">
+        <f t="shared" si="4"/>
+        <v>2928851</v>
+      </c>
+      <c r="M11" s="71">
+        <f t="shared" si="0"/>
+        <v>4216954</v>
+      </c>
+      <c r="N11" s="76">
+        <f t="shared" si="5"/>
+        <v>15983565</v>
+      </c>
+      <c r="O11" s="71">
         <f t="shared" si="1"/>
-        <v>1133101</v>
-      </c>
-      <c r="K11" s="72">
-        <f t="shared" si="2"/>
-        <v>1795750</v>
-      </c>
-      <c r="L11" s="72">
-        <f t="shared" si="3"/>
-        <v>4216954</v>
-      </c>
-      <c r="M11" s="77">
-        <f t="shared" si="4"/>
-        <v>2798759</v>
-      </c>
-      <c r="N11" s="72">
-        <f t="shared" si="5"/>
-        <v>4435503</v>
-      </c>
-      <c r="O11" s="77">
+        <v>7234262</v>
+      </c>
+      <c r="P11" s="76">
         <f t="shared" si="6"/>
-        <v>12844304</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>68533979</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="68" t="s">
         <v>255</v>
       </c>
       <c r="B12" s="67">
         <v>2024</v>
       </c>
-      <c r="C12" s="74">
+      <c r="C12" s="73">
         <v>4640922</v>
       </c>
-      <c r="D12" s="74">
+      <c r="D12" s="73">
         <v>797680</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E12" s="73">
         <v>67612</v>
       </c>
-      <c r="F12" s="74">
+      <c r="F12" s="73">
         <v>1267032</v>
       </c>
-      <c r="G12" s="74">
+      <c r="G12" s="73">
         <v>1884367</v>
       </c>
-      <c r="H12" s="74">
+      <c r="H12" s="73">
         <v>624231</v>
       </c>
-      <c r="I12" s="72">
-        <f t="shared" si="0"/>
+      <c r="I12" s="73">
+        <v>0</v>
+      </c>
+      <c r="J12" s="71">
+        <f t="shared" si="2"/>
         <v>1489523</v>
       </c>
-      <c r="J12" s="72">
+      <c r="K12" s="71">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="71">
+        <f t="shared" si="4"/>
+        <v>3151399</v>
+      </c>
+      <c r="M12" s="71">
+        <f t="shared" si="0"/>
+        <v>3679122</v>
+      </c>
+      <c r="N12" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="71">
         <f t="shared" si="1"/>
-        <v>1267032</v>
-      </c>
-      <c r="K12" s="72">
-        <f t="shared" si="2"/>
-        <v>1884367</v>
-      </c>
-      <c r="L12" s="72">
-        <f t="shared" si="3"/>
-        <v>3679122</v>
-      </c>
-      <c r="M12" s="77">
-        <f t="shared" si="4"/>
-        <v>3129569</v>
-      </c>
-      <c r="N12" s="72">
-        <f t="shared" si="5"/>
-        <v>4654386</v>
-      </c>
-      <c r="O12" s="77">
+        <v>7783956</v>
+      </c>
+      <c r="P12" s="76">
         <f t="shared" si="6"/>
-        <v>15973873</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>68533979</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="68" t="s">
         <v>255</v>
       </c>
       <c r="B13" s="67">
         <v>2025</v>
       </c>
-      <c r="C13" s="74">
+      <c r="C13" s="73">
         <v>3563000</v>
       </c>
-      <c r="D13" s="74">
+      <c r="D13" s="73">
         <v>830000</v>
       </c>
-      <c r="E13" s="73">
-        <f>E12/SUM($E12:$H12)*($C$13-$D$13)</f>
+      <c r="E13" s="72">
         <v>48080.135468960842</v>
       </c>
-      <c r="F13" s="73">
-        <f>F12/SUM($E12:$H12)*($C$13-$D$13)</f>
+      <c r="F13" s="72">
         <v>901009.73501018144</v>
       </c>
-      <c r="G13" s="73">
-        <f>G12/SUM($E12:$H12)*($C$13-$D$13)</f>
+      <c r="G13" s="72">
         <v>1340007.9961136978</v>
       </c>
-      <c r="H13" s="73">
-        <f>H12/SUM($E12:$H12)*($C$13-$D$13)</f>
+      <c r="H13" s="72">
         <v>443902.13340715988</v>
       </c>
       <c r="I13" s="72">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="71">
+        <f t="shared" si="2"/>
         <v>1321982.2688761207</v>
       </c>
-      <c r="J13" s="72">
+      <c r="K13" s="71">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="71">
+        <f t="shared" si="4"/>
+        <v>2241017.7311238791</v>
+      </c>
+      <c r="M13" s="71">
+        <f t="shared" si="0"/>
+        <v>3265296</v>
+      </c>
+      <c r="N13" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="71">
         <f t="shared" si="1"/>
-        <v>901009.73501018144</v>
-      </c>
-      <c r="K13" s="72">
-        <f t="shared" si="2"/>
-        <v>1340007.9961136978</v>
-      </c>
-      <c r="L13" s="72">
-        <f t="shared" si="3"/>
-        <v>3265296</v>
-      </c>
-      <c r="M13" s="77">
-        <f t="shared" si="4"/>
-        <v>2225494</v>
-      </c>
-      <c r="N13" s="72">
-        <f t="shared" si="5"/>
-        <v>3309820</v>
-      </c>
-      <c r="O13" s="77">
+        <v>5535314</v>
+      </c>
+      <c r="P13" s="76">
         <f t="shared" si="6"/>
-        <v>18199367</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="M14" s="78"/>
-      <c r="O14" s="79"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="101" t="s">
+        <v>68533979</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="N14" s="77"/>
+      <c r="P14" s="78"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="169" t="s">
         <v>262</v>
       </c>
-      <c r="B15" s="101"/>
-      <c r="C15" s="72">
+      <c r="B15" s="169"/>
+      <c r="C15" s="71">
         <f t="shared" ref="C15:H15" si="7">MAX(C3:C13,1.25*MAX(C8:C13))</f>
         <v>8667120</v>
       </c>
-      <c r="D15" s="72">
+      <c r="D15" s="71">
         <f t="shared" si="7"/>
-        <v>4362589</v>
-      </c>
-      <c r="E15" s="72">
+        <v>4361827</v>
+      </c>
+      <c r="E15" s="71">
         <f t="shared" si="7"/>
         <v>215298.75</v>
       </c>
-      <c r="F15" s="72">
+      <c r="F15" s="71">
         <f t="shared" si="7"/>
         <v>2218260</v>
       </c>
-      <c r="G15" s="72">
+      <c r="G15" s="71">
         <f t="shared" si="7"/>
         <v>2355458.75</v>
       </c>
-      <c r="H15" s="72">
+      <c r="H15" s="71">
         <f t="shared" si="7"/>
         <v>782388.75</v>
       </c>
-      <c r="I15" s="72">
-        <f t="shared" ref="I15:K15" si="8">ROUND(MAX(I3:I13,1.25*MAX(I8:I13)),0)</f>
-        <v>4791484</v>
-      </c>
-      <c r="J15" s="72">
+      <c r="I15" s="71"/>
+      <c r="J15" s="71">
+        <f t="shared" ref="J15:K15" si="8">ROUND(MAX(J3:J13,1.25*MAX(J8:J13)),0)</f>
+        <v>4789794</v>
+      </c>
+      <c r="K15" s="71">
         <f t="shared" si="8"/>
-        <v>2218260</v>
-      </c>
-      <c r="K15" s="72">
-        <f t="shared" si="8"/>
-        <v>2355459</v>
-      </c>
-      <c r="L15" s="72">
+        <v>11394780</v>
+      </c>
+      <c r="L15" s="71">
         <f>ROUND(MAX(L3:L13,1.25*MAX(L8:L13)),0)</f>
-        <v>11834965</v>
-      </c>
-      <c r="M15" s="77">
-        <f t="shared" ref="M15:N15" si="9">ROUND(MAX(M3:M13,1.25*MAX(M8:M13)),0)</f>
-        <v>5479103</v>
-      </c>
-      <c r="N15" s="72">
+        <v>4242820</v>
+      </c>
+      <c r="M15" s="71">
+        <f>ROUND(MAX(M3:M13,1.25*MAX(M8:M13)),0)</f>
+        <v>11830791</v>
+      </c>
+      <c r="N15" s="76">
+        <f t="shared" ref="N15:O15" si="9">ROUND(MAX(N3:N13,1.25*MAX(N8:N13)),0)</f>
+        <v>28145106</v>
+      </c>
+      <c r="O15" s="71">
         <f t="shared" si="9"/>
-        <v>5817983</v>
-      </c>
-      <c r="O15" s="77">
-        <f>_xlfn.FORECAST.LINEAR(2060,O8:O13,B8:B13)</f>
-        <v>115943144.28571415</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="63">
-      <c r="A17" s="99" t="s">
+        <v>10479765</v>
+      </c>
+      <c r="P15" s="76">
+        <f>_xlfn.FORECAST.LINEAR(2060,P8:P13,B8:B13)</f>
+        <v>413751720.95238495</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="63">
+      <c r="A17" s="167" t="s">
         <v>261</v>
       </c>
-      <c r="B17" s="99"/>
-      <c r="C17" s="71" t="s">
+      <c r="B17" s="167"/>
+      <c r="C17" s="70" t="s">
         <v>259</v>
       </c>
-      <c r="D17" s="71" t="s">
+      <c r="D17" s="70" t="s">
         <v>258</v>
       </c>
-      <c r="E17" s="71" t="s">
+      <c r="E17" s="70" t="s">
         <v>257</v>
       </c>
       <c r="F17" s="65"/>
-      <c r="G17" s="100" t="s">
+      <c r="L17" s="168" t="s">
         <v>260</v>
       </c>
-      <c r="H17" s="100" t="s">
+      <c r="M17" s="168" t="s">
         <v>259</v>
       </c>
-      <c r="I17" s="100" t="s">
+      <c r="N17" s="168" t="s">
         <v>258</v>
       </c>
-      <c r="J17" s="100" t="s">
+      <c r="O17" s="168" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:15">
       <c r="A18" s="68" t="s">
         <v>255</v>
       </c>
@@ -9941,24 +15291,24 @@
         <v>2015</v>
       </c>
       <c r="C18" s="66">
-        <f t="shared" ref="C18:C28" si="10">ROUND(I3/I$15,6)</f>
+        <f t="shared" ref="C18:C28" si="10">ROUND(J3/J$15,6)</f>
         <v>1</v>
       </c>
       <c r="D18" s="66">
-        <f t="shared" ref="D18:D28" si="11">ROUND(J3/J$15,6)</f>
-        <v>0.97052499999999997</v>
+        <f>ROUND(K3/K$15,6)</f>
+        <v>0.68562999999999996</v>
       </c>
       <c r="E18" s="66">
-        <f t="shared" ref="E18:E28" si="12">ROUND(K3/K$15,6)</f>
-        <v>0.31388100000000002</v>
+        <f t="shared" ref="E18:E28" si="11">ROUND(L3/L$15,6)</f>
+        <v>0.68167199999999994</v>
       </c>
       <c r="F18" s="65"/>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="100"/>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" s="168"/>
+      <c r="M18" s="168"/>
+      <c r="N18" s="168"/>
+      <c r="O18" s="168"/>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="68" t="s">
         <v>255</v>
       </c>
@@ -9967,23 +15317,23 @@
       </c>
       <c r="C19" s="66">
         <f t="shared" si="10"/>
-        <v>0.88882300000000003</v>
+        <v>0.88913699999999996</v>
       </c>
       <c r="D19" s="66">
+        <f t="shared" ref="D19:D28" si="12">ROUND(K4/K$15,6)</f>
+        <v>0.74599099999999996</v>
+      </c>
+      <c r="E19" s="66">
         <f t="shared" si="11"/>
-        <v>0.88070700000000002</v>
-      </c>
-      <c r="E19" s="66">
-        <f t="shared" si="12"/>
-        <v>0.42076200000000002</v>
+        <v>0.69404900000000003</v>
       </c>
       <c r="F19" s="65"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="100"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="100"/>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" s="168"/>
+      <c r="M19" s="168"/>
+      <c r="N19" s="168"/>
+      <c r="O19" s="168"/>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="68" t="s">
         <v>255</v>
       </c>
@@ -9992,23 +15342,23 @@
       </c>
       <c r="C20" s="66">
         <f t="shared" si="10"/>
-        <v>0.98978699999999997</v>
+        <v>0.99013600000000002</v>
       </c>
       <c r="D20" s="66">
+        <f>ROUND(K5/K$15,6)</f>
+        <v>0.77723299999999995</v>
+      </c>
+      <c r="E20" s="66">
         <f t="shared" si="11"/>
-        <v>0.747058</v>
-      </c>
-      <c r="E20" s="66">
-        <f t="shared" si="12"/>
-        <v>0.54383999999999999</v>
+        <v>0.69250199999999995</v>
       </c>
       <c r="F20" s="65"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="100"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="100"/>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" s="168"/>
+      <c r="M20" s="168"/>
+      <c r="N20" s="168"/>
+      <c r="O20" s="168"/>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="68" t="s">
         <v>255</v>
       </c>
@@ -10017,23 +15367,23 @@
       </c>
       <c r="C21" s="66">
         <f t="shared" si="10"/>
-        <v>0.873475</v>
+        <v>0.87378299999999998</v>
       </c>
       <c r="D21" s="66">
+        <f t="shared" si="12"/>
+        <v>0.76139699999999999</v>
+      </c>
+      <c r="E21" s="66">
         <f t="shared" si="11"/>
-        <v>0.80471499999999996</v>
-      </c>
-      <c r="E21" s="66">
-        <f t="shared" si="12"/>
-        <v>0.56429200000000002</v>
+        <v>0.73400100000000001</v>
       </c>
       <c r="F21" s="65"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="100"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="100"/>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21" s="168"/>
+      <c r="M21" s="168"/>
+      <c r="N21" s="168"/>
+      <c r="O21" s="168"/>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="68" t="s">
         <v>255</v>
       </c>
@@ -10042,32 +15392,31 @@
       </c>
       <c r="C22" s="66">
         <f t="shared" si="10"/>
-        <v>0.82523599999999997</v>
+        <v>0.82552700000000001</v>
       </c>
       <c r="D22" s="66">
+        <f t="shared" si="12"/>
+        <v>0.74398900000000001</v>
+      </c>
+      <c r="E22" s="66">
         <f t="shared" si="11"/>
-        <v>0.85576700000000006</v>
-      </c>
-      <c r="E22" s="66">
-        <f t="shared" si="12"/>
-        <v>0.65289900000000001</v>
+        <v>0.80988400000000005</v>
       </c>
       <c r="F22" s="65"/>
-      <c r="G22" s="100"/>
-      <c r="H22" s="70">
+      <c r="L22" s="168"/>
+      <c r="M22" s="69">
         <f>MAX(C$23:C$28)</f>
-        <v>0.73869399999999996</v>
-      </c>
-      <c r="I22" s="81">
+        <v>0.73895500000000003</v>
+      </c>
+      <c r="N22" s="80">
         <v>1</v>
       </c>
-      <c r="J22" s="70">
+      <c r="O22" s="69">
         <f>MAX(E$23:E$28)</f>
         <v>0.8</v>
       </c>
-      <c r="K22" s="69"/>
-    </row>
-    <row r="23" spans="1:11">
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="68" t="s">
         <v>255</v>
       </c>
@@ -10076,34 +15425,34 @@
       </c>
       <c r="C23" s="66">
         <f t="shared" si="10"/>
-        <v>0.73869399999999996</v>
+        <v>0.73895500000000003</v>
       </c>
       <c r="D23" s="66">
+        <f t="shared" si="12"/>
+        <v>0.8</v>
+      </c>
+      <c r="E23" s="66">
         <f t="shared" si="11"/>
         <v>0.8</v>
       </c>
-      <c r="E23" s="66">
-        <f t="shared" si="12"/>
-        <v>0.68761499999999998</v>
-      </c>
       <c r="F23" s="65"/>
-      <c r="G23" s="94" t="s">
+      <c r="L23" s="162" t="s">
         <v>256</v>
       </c>
-      <c r="H23" s="64">
-        <f t="shared" ref="H23:J28" si="13">ROUND(C23/H$22,6)</f>
+      <c r="M23" s="64">
+        <f t="shared" ref="M23:M28" si="13">ROUND(C23/M$22,6)</f>
         <v>1</v>
       </c>
-      <c r="I23" s="82">
-        <f>O8/O$15</f>
-        <v>3.78054435818857E-2</v>
-      </c>
-      <c r="J23" s="64">
-        <f t="shared" si="13"/>
-        <v>0.85951900000000003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="N23" s="81">
+        <f t="shared" ref="N23:N28" si="14">P8/P$15</f>
+        <v>5.4419314433718523E-2</v>
+      </c>
+      <c r="O23" s="64">
+        <f t="shared" ref="O23:O28" si="15">ROUND(E23/O$22,6)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="68" t="s">
         <v>255</v>
       </c>
@@ -10112,32 +15461,32 @@
       </c>
       <c r="C24" s="66">
         <f t="shared" si="10"/>
-        <v>0.31470999999999999</v>
+        <v>0.31482100000000002</v>
       </c>
       <c r="D24" s="66">
+        <f t="shared" si="12"/>
+        <v>0.56360299999999997</v>
+      </c>
+      <c r="E24" s="66">
         <f t="shared" si="11"/>
-        <v>0.55678700000000003</v>
-      </c>
-      <c r="E24" s="66">
-        <f t="shared" si="12"/>
-        <v>0.42936400000000002</v>
+        <v>0.52947</v>
       </c>
       <c r="F24" s="65"/>
-      <c r="G24" s="95"/>
-      <c r="H24" s="64">
+      <c r="L24" s="163"/>
+      <c r="M24" s="64">
         <f t="shared" si="13"/>
-        <v>0.42603600000000003</v>
-      </c>
-      <c r="I24" s="82">
-        <f t="shared" ref="I24:I28" si="14">O9/O$15</f>
-        <v>6.4117408974874349E-2</v>
-      </c>
-      <c r="J24" s="64">
-        <f t="shared" si="13"/>
-        <v>0.53670499999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>0.426035</v>
+      </c>
+      <c r="N24" s="81">
+        <f t="shared" si="14"/>
+        <v>9.2757932007288671E-2</v>
+      </c>
+      <c r="O24" s="64">
+        <f t="shared" si="15"/>
+        <v>0.66183800000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="68" t="s">
         <v>255</v>
       </c>
@@ -10146,32 +15495,32 @@
       </c>
       <c r="C25" s="66">
         <f t="shared" si="10"/>
-        <v>0.32610699999999998</v>
+        <v>0.32622200000000001</v>
       </c>
       <c r="D25" s="66">
+        <f t="shared" si="12"/>
+        <v>0.503521</v>
+      </c>
+      <c r="E25" s="66">
         <f t="shared" si="11"/>
-        <v>0.47664200000000001</v>
-      </c>
-      <c r="E25" s="66">
-        <f t="shared" si="12"/>
-        <v>0.67202799999999996</v>
+        <v>0.62228700000000003</v>
       </c>
       <c r="F25" s="65"/>
-      <c r="G25" s="95"/>
-      <c r="H25" s="64">
+      <c r="L25" s="163"/>
+      <c r="M25" s="64">
         <f t="shared" si="13"/>
         <v>0.44146400000000002</v>
       </c>
-      <c r="I25" s="82">
+      <c r="N25" s="81">
         <f t="shared" si="14"/>
-        <v>8.6641992175450724E-2</v>
-      </c>
-      <c r="J25" s="64">
-        <f t="shared" si="13"/>
-        <v>0.84003499999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>0.12700953576468041</v>
+      </c>
+      <c r="O25" s="64">
+        <f t="shared" si="15"/>
+        <v>0.77785899999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="68" t="s">
         <v>255</v>
       </c>
@@ -10180,32 +15529,32 @@
       </c>
       <c r="C26" s="66">
         <f t="shared" si="10"/>
-        <v>0.35631299999999999</v>
+        <v>0.35643900000000001</v>
       </c>
       <c r="D26" s="66">
+        <f t="shared" si="12"/>
+        <v>0.56789900000000004</v>
+      </c>
+      <c r="E26" s="66">
         <f t="shared" si="11"/>
-        <v>0.51080599999999998</v>
-      </c>
-      <c r="E26" s="66">
-        <f t="shared" si="12"/>
-        <v>0.762378</v>
+        <v>0.69030800000000003</v>
       </c>
       <c r="F26" s="65"/>
-      <c r="G26" s="95"/>
-      <c r="H26" s="64">
+      <c r="L26" s="163"/>
+      <c r="M26" s="64">
         <f t="shared" si="13"/>
         <v>0.48235499999999998</v>
       </c>
-      <c r="I26" s="82">
+      <c r="N26" s="81">
         <f t="shared" si="14"/>
-        <v>0.11078105634558508</v>
-      </c>
-      <c r="J26" s="64">
-        <f t="shared" si="13"/>
-        <v>0.95297299999999996</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>0.16564034789328883</v>
+      </c>
+      <c r="O26" s="64">
+        <f t="shared" si="15"/>
+        <v>0.86288500000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="68" t="s">
         <v>255</v>
       </c>
@@ -10214,32 +15563,32 @@
       </c>
       <c r="C27" s="66">
         <f t="shared" si="10"/>
-        <v>0.31086900000000001</v>
+        <v>0.31097900000000001</v>
       </c>
       <c r="D27" s="66">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="E27" s="66">
         <f t="shared" si="11"/>
-        <v>0.571183</v>
-      </c>
-      <c r="E27" s="66">
-        <f t="shared" si="12"/>
-        <v>0.8</v>
+        <v>0.74275999999999998</v>
       </c>
       <c r="F27" s="65"/>
-      <c r="G27" s="95"/>
-      <c r="H27" s="64">
+      <c r="L27" s="163"/>
+      <c r="M27" s="64">
         <f t="shared" si="13"/>
         <v>0.42083599999999999</v>
       </c>
-      <c r="I27" s="82">
+      <c r="N27" s="81">
         <f t="shared" si="14"/>
-        <v>0.13777332931937925</v>
-      </c>
-      <c r="J27" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>0.16564034789328883</v>
+      </c>
+      <c r="O27" s="64">
+        <f t="shared" si="15"/>
+        <v>0.92845</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="68" t="s">
         <v>255</v>
       </c>
@@ -10248,29 +15597,29 @@
       </c>
       <c r="C28" s="66">
         <f t="shared" si="10"/>
-        <v>0.27590199999999998</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="D28" s="66">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="E28" s="66">
         <f t="shared" si="11"/>
-        <v>0.40617900000000001</v>
-      </c>
-      <c r="E28" s="66">
-        <f t="shared" si="12"/>
-        <v>0.56889500000000004</v>
+        <v>0.52819099999999997</v>
       </c>
       <c r="F28" s="65"/>
-      <c r="G28" s="96"/>
-      <c r="H28" s="64">
+      <c r="L28" s="164"/>
+      <c r="M28" s="64">
         <f t="shared" si="13"/>
         <v>0.3735</v>
       </c>
-      <c r="I28" s="82">
+      <c r="N28" s="81">
         <f t="shared" si="14"/>
-        <v>0.15696803042663748</v>
-      </c>
-      <c r="J28" s="64">
-        <f t="shared" si="13"/>
-        <v>0.71111899999999995</v>
+        <v>0.16564034789328883</v>
+      </c>
+      <c r="O28" s="64">
+        <f t="shared" si="15"/>
+        <v>0.66023900000000002</v>
       </c>
     </row>
   </sheetData>
@@ -10280,20 +15629,20 @@
     </sortState>
   </autoFilter>
   <mergeCells count="12">
-    <mergeCell ref="J17:J21"/>
+    <mergeCell ref="O17:O21"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:K1"/>
-    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="D1:L1"/>
+    <mergeCell ref="M1:O1"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="I17:I21"/>
-    <mergeCell ref="G23:G28"/>
+    <mergeCell ref="N17:N21"/>
+    <mergeCell ref="L23:L28"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="G17:G22"/>
-    <mergeCell ref="H17:H21"/>
+    <mergeCell ref="L17:L22"/>
+    <mergeCell ref="M17:M21"/>
   </mergeCells>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="C18:E28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -10311,7 +15660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2D035B-9392-44AC-8A8E-7EF18C2802D4}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:N204"/>
@@ -16476,12 +21825,12 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
@@ -16809,176 +22158,176 @@
         <v>143</v>
       </c>
       <c r="B3">
-        <f>Calculation!$L$15</f>
-        <v>11834965</v>
+        <f>Calculation!$M$15</f>
+        <v>11830791</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:R7" si="1">$B3</f>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="D3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="E3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="F3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="G3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="H3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="I3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="J3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="K3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="L3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="M3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="N3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="O3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="P3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="Q3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="R3">
         <f t="shared" si="1"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="S3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="T3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="U3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="V3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="W3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="X3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="Y3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="Z3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AA3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AB3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AC3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AD3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AE3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AF3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AG3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AH3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AI3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AJ3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AK3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AL3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AM3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AN3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AO3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AP3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AQ3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
       <c r="AR3">
         <f t="shared" si="0"/>
-        <v>11834965</v>
+        <v>11830791</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -16986,169 +22335,176 @@
         <v>144</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <f>Calculation!N15</f>
+        <v>28145106</v>
       </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" cm="1">
-        <f t="array" ref="D4:I4">TRANSPOSE(Calculation!O8:O13)</f>
-        <v>4383282</v>
+        <f>$B4</f>
+        <v>28145106</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="E4">
-        <v>7433974</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="F4">
-        <v>10045545</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="G4">
-        <v>12844304</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="H4">
-        <v>15973873</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="I4">
-        <v>18199367</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="J4">
-        <f>_xlfn.FORECAST.LINEAR(J$1,_xlfn.ANCHORARRAY($D4),$D$1:$I$1)</f>
-        <v>21229945.600000381</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:AR4" si="2">_xlfn.FORECAST.LINEAR(K$1,_xlfn.ANCHORARRAY($D4),$D$1:$I$1)</f>
-        <v>24015627.91428566</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="L4">
-        <f t="shared" si="2"/>
-        <v>26801310.228571892</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="M4">
-        <f t="shared" si="2"/>
-        <v>29586992.54285717</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="N4">
-        <f t="shared" si="2"/>
-        <v>32372674.857143402</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="O4">
-        <f t="shared" si="2"/>
-        <v>35158357.17142868</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="P4">
-        <f t="shared" si="2"/>
-        <v>37944039.485714912</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="2"/>
-        <v>40729721.800000191</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="R4">
-        <f t="shared" si="2"/>
-        <v>43515404.114286423</v>
+        <f t="shared" si="1"/>
+        <v>28145106</v>
       </c>
       <c r="S4">
-        <f t="shared" si="2"/>
-        <v>46301086.428571701</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="T4">
-        <f t="shared" si="2"/>
-        <v>49086768.742857933</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="U4">
-        <f t="shared" si="2"/>
-        <v>51872451.057143211</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="V4">
-        <f t="shared" si="2"/>
-        <v>54658133.37142849</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="W4">
-        <f t="shared" si="2"/>
-        <v>57443815.685714722</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="X4">
-        <f t="shared" si="2"/>
-        <v>60229498</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="2"/>
-        <v>63015180.314286232</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="2"/>
-        <v>65800862.62857151</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="2"/>
-        <v>68586544.942857742</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="2"/>
-        <v>71372227.257143021</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AC4">
-        <f t="shared" si="2"/>
-        <v>74157909.571429253</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AD4">
-        <f t="shared" si="2"/>
-        <v>76943591.885714531</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AE4">
-        <f t="shared" si="2"/>
-        <v>79729274.200000763</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AF4">
-        <f t="shared" si="2"/>
-        <v>82514956.514286041</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="2"/>
-        <v>85300638.82857132</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AH4">
-        <f t="shared" si="2"/>
-        <v>88086321.142857552</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="2"/>
-        <v>90872003.45714283</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AJ4">
-        <f t="shared" si="2"/>
-        <v>93657685.771429062</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AK4">
-        <f t="shared" si="2"/>
-        <v>96443368.08571434</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AL4">
-        <f t="shared" si="2"/>
-        <v>99229050.400000572</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AM4">
-        <f t="shared" si="2"/>
-        <v>102014732.71428585</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AN4">
-        <f t="shared" si="2"/>
-        <v>104800415.02857208</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AO4">
-        <f t="shared" si="2"/>
-        <v>107586097.34285736</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AP4">
-        <f t="shared" si="2"/>
-        <v>110371779.65714359</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AQ4">
-        <f t="shared" si="2"/>
-        <v>113157461.97142887</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
       <c r="AR4">
-        <f t="shared" si="2"/>
-        <v>115943144.28571415</v>
+        <f t="shared" si="0"/>
+        <v>28145106</v>
       </c>
     </row>
     <row r="5" spans="1:44">
@@ -17508,176 +22864,176 @@
         <v>147</v>
       </c>
       <c r="B7">
-        <f>Calculation!$N$15</f>
-        <v>5817983</v>
+        <f>Calculation!$O$15</f>
+        <v>10479765</v>
       </c>
       <c r="C7">
         <f t="shared" si="1"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AK7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AL7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AM7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AN7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AO7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AP7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AQ7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
       <c r="AR7">
         <f t="shared" si="0"/>
-        <v>5817983</v>
+        <v>10479765</v>
       </c>
     </row>
     <row r="11" spans="1:44">
@@ -17745,7 +23101,7 @@
       <c r="C49" s="41"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>